--- a/template_vierge.xlsx
+++ b/template_vierge.xlsx
@@ -10,11 +10,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISEZ-MOI" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paramètres" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Salles spéciales" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Professeurs" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Services" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Disponibilités" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contraintes" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Professeurs" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Services" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Disponibilités" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contraintes" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2018,287 +2017,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>SALLES SPÉCIALES</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Uniquement les salles particulières partagées entre plusieurs classes (laboratoires, salle informatique, terrain de sport…). Inutile de lister les salles de classe ordinaires.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>Nom de la salle</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="inlineStr">
-        <is>
-          <t>Capacité</t>
-        </is>
-      </c>
-      <c r="D3" s="12" t="inlineStr">
-        <is>
-          <t>Remarques</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="16" t="inlineStr">
-        <is>
-          <t>Labo SVT</t>
-        </is>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>Laboratoire SVT</t>
-        </is>
-      </c>
-      <c r="C4" s="16" t="n">
-        <v>35</v>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
-        <is>
-          <t>TP de SVT uniquement</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="16" t="inlineStr">
-        <is>
-          <t>Labo PC</t>
-        </is>
-      </c>
-      <c r="B5" s="16" t="inlineStr">
-        <is>
-          <t>Laboratoire Physique-Chimie</t>
-        </is>
-      </c>
-      <c r="C5" s="16" t="n">
-        <v>35</v>
-      </c>
-      <c r="D5" s="16" t="inlineStr">
-        <is>
-          <t>TP de Physique-Chimie</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>Salle Info</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>Salle informatique</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="n">
-        <v>30</v>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>20 postes disponibles</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>Terrain EPS</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>Terrain EPS</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr"/>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>Terrain extérieur, indisponible quand il pleut fort</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="n"/>
-      <c r="B8" s="7" t="n"/>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="n"/>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="n"/>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="n"/>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="n"/>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="n"/>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="n"/>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="n"/>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="n"/>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="n"/>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="n"/>
-      <c r="B20" s="7" t="n"/>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="n"/>
-      <c r="B21" s="7" t="n"/>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="n"/>
-      <c r="B22" s="7" t="n"/>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="n"/>
-      <c r="B23" s="7" t="n"/>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="n"/>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="7" t="n"/>
-      <c r="D24" s="7" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="n"/>
-      <c r="B25" s="7" t="n"/>
-      <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="n"/>
-      <c r="B26" s="7" t="n"/>
-      <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="n"/>
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="n"/>
-      <c r="B28" s="7" t="n"/>
-      <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="n"/>
-      <c r="B29" s="7" t="n"/>
-      <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="n"/>
-      <c r="B30" s="7" t="n"/>
-      <c r="C30" s="7" t="n"/>
-      <c r="D30" s="7" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="B4:B30" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Choisissez une valeur dans la liste" type="list">
-      <formula1>"Laboratoire SVT,Laboratoire Physique-Chimie,Salle informatique,Terrain EPS,Bibliothèque/CDI,Autre"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:F120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3306,13 +3024,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F400"/>
+  <dimension ref="A1:E400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3360,11 +3078,6 @@
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>Taille du bloc (optionnel)</t>
-        </is>
-      </c>
-      <c r="F3" s="12" t="inlineStr">
-        <is>
           <t>Jour imposé (optionnel)</t>
         </is>
       </c>
@@ -3375,7 +3088,6 @@
       <c r="C4" s="16" t="n"/>
       <c r="D4" s="16" t="n"/>
       <c r="E4" s="16" t="n"/>
-      <c r="F4" s="16" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="16" t="n"/>
@@ -3383,7 +3095,6 @@
       <c r="C5" s="16" t="n"/>
       <c r="D5" s="16" t="n"/>
       <c r="E5" s="16" t="n"/>
-      <c r="F5" s="16" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="16" t="n"/>
@@ -3391,7 +3102,6 @@
       <c r="C6" s="16" t="n"/>
       <c r="D6" s="16" t="n"/>
       <c r="E6" s="16" t="n"/>
-      <c r="F6" s="16" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="16" t="n"/>
@@ -3399,7 +3109,6 @@
       <c r="C7" s="16" t="n"/>
       <c r="D7" s="16" t="n"/>
       <c r="E7" s="16" t="n"/>
-      <c r="F7" s="16" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="16" t="n"/>
@@ -3407,7 +3116,6 @@
       <c r="C8" s="16" t="n"/>
       <c r="D8" s="16" t="n"/>
       <c r="E8" s="16" t="n"/>
-      <c r="F8" s="16" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="16" t="n"/>
@@ -3415,7 +3123,6 @@
       <c r="C9" s="16" t="n"/>
       <c r="D9" s="16" t="n"/>
       <c r="E9" s="16" t="n"/>
-      <c r="F9" s="16" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="16" t="n"/>
@@ -3423,7 +3130,6 @@
       <c r="C10" s="16" t="n"/>
       <c r="D10" s="16" t="n"/>
       <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="16" t="n"/>
@@ -3431,7 +3137,6 @@
       <c r="C11" s="16" t="n"/>
       <c r="D11" s="16" t="n"/>
       <c r="E11" s="16" t="n"/>
-      <c r="F11" s="16" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="16" t="n"/>
@@ -3439,7 +3144,6 @@
       <c r="C12" s="16" t="n"/>
       <c r="D12" s="16" t="n"/>
       <c r="E12" s="16" t="n"/>
-      <c r="F12" s="16" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="16" t="n"/>
@@ -3447,7 +3151,6 @@
       <c r="C13" s="16" t="n"/>
       <c r="D13" s="16" t="n"/>
       <c r="E13" s="16" t="n"/>
-      <c r="F13" s="16" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="16" t="n"/>
@@ -3455,7 +3158,6 @@
       <c r="C14" s="16" t="n"/>
       <c r="D14" s="16" t="n"/>
       <c r="E14" s="16" t="n"/>
-      <c r="F14" s="16" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="16" t="n"/>
@@ -3463,7 +3165,6 @@
       <c r="C15" s="16" t="n"/>
       <c r="D15" s="16" t="n"/>
       <c r="E15" s="16" t="n"/>
-      <c r="F15" s="16" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="16" t="n"/>
@@ -3471,7 +3172,6 @@
       <c r="C16" s="16" t="n"/>
       <c r="D16" s="16" t="n"/>
       <c r="E16" s="16" t="n"/>
-      <c r="F16" s="16" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="16" t="n"/>
@@ -3479,7 +3179,6 @@
       <c r="C17" s="16" t="n"/>
       <c r="D17" s="16" t="n"/>
       <c r="E17" s="16" t="n"/>
-      <c r="F17" s="16" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="16" t="n"/>
@@ -3487,7 +3186,6 @@
       <c r="C18" s="16" t="n"/>
       <c r="D18" s="16" t="n"/>
       <c r="E18" s="16" t="n"/>
-      <c r="F18" s="16" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="16" t="n"/>
@@ -3495,7 +3193,6 @@
       <c r="C19" s="16" t="n"/>
       <c r="D19" s="16" t="n"/>
       <c r="E19" s="16" t="n"/>
-      <c r="F19" s="16" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="16" t="n"/>
@@ -3503,7 +3200,6 @@
       <c r="C20" s="16" t="n"/>
       <c r="D20" s="16" t="n"/>
       <c r="E20" s="16" t="n"/>
-      <c r="F20" s="16" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="16" t="n"/>
@@ -3511,7 +3207,6 @@
       <c r="C21" s="16" t="n"/>
       <c r="D21" s="16" t="n"/>
       <c r="E21" s="16" t="n"/>
-      <c r="F21" s="16" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="16" t="n"/>
@@ -3519,7 +3214,6 @@
       <c r="C22" s="16" t="n"/>
       <c r="D22" s="16" t="n"/>
       <c r="E22" s="16" t="n"/>
-      <c r="F22" s="16" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="16" t="n"/>
@@ -3527,7 +3221,6 @@
       <c r="C23" s="16" t="n"/>
       <c r="D23" s="16" t="n"/>
       <c r="E23" s="16" t="n"/>
-      <c r="F23" s="16" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="16" t="n"/>
@@ -3535,7 +3228,6 @@
       <c r="C24" s="16" t="n"/>
       <c r="D24" s="16" t="n"/>
       <c r="E24" s="16" t="n"/>
-      <c r="F24" s="16" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="16" t="n"/>
@@ -3543,7 +3235,6 @@
       <c r="C25" s="16" t="n"/>
       <c r="D25" s="16" t="n"/>
       <c r="E25" s="16" t="n"/>
-      <c r="F25" s="16" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="16" t="n"/>
@@ -3551,7 +3242,6 @@
       <c r="C26" s="16" t="n"/>
       <c r="D26" s="16" t="n"/>
       <c r="E26" s="16" t="n"/>
-      <c r="F26" s="16" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="16" t="n"/>
@@ -3559,7 +3249,6 @@
       <c r="C27" s="16" t="n"/>
       <c r="D27" s="16" t="n"/>
       <c r="E27" s="16" t="n"/>
-      <c r="F27" s="16" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="16" t="n"/>
@@ -3567,7 +3256,6 @@
       <c r="C28" s="16" t="n"/>
       <c r="D28" s="16" t="n"/>
       <c r="E28" s="16" t="n"/>
-      <c r="F28" s="16" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="16" t="n"/>
@@ -3575,7 +3263,6 @@
       <c r="C29" s="16" t="n"/>
       <c r="D29" s="16" t="n"/>
       <c r="E29" s="16" t="n"/>
-      <c r="F29" s="16" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="16" t="n"/>
@@ -3583,7 +3270,6 @@
       <c r="C30" s="16" t="n"/>
       <c r="D30" s="16" t="n"/>
       <c r="E30" s="16" t="n"/>
-      <c r="F30" s="16" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="16" t="n"/>
@@ -3591,7 +3277,6 @@
       <c r="C31" s="16" t="n"/>
       <c r="D31" s="16" t="n"/>
       <c r="E31" s="16" t="n"/>
-      <c r="F31" s="16" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="16" t="n"/>
@@ -3599,7 +3284,6 @@
       <c r="C32" s="16" t="n"/>
       <c r="D32" s="16" t="n"/>
       <c r="E32" s="16" t="n"/>
-      <c r="F32" s="16" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="16" t="n"/>
@@ -3607,7 +3291,6 @@
       <c r="C33" s="16" t="n"/>
       <c r="D33" s="16" t="n"/>
       <c r="E33" s="16" t="n"/>
-      <c r="F33" s="16" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="16" t="n"/>
@@ -3615,7 +3298,6 @@
       <c r="C34" s="16" t="n"/>
       <c r="D34" s="16" t="n"/>
       <c r="E34" s="16" t="n"/>
-      <c r="F34" s="16" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="16" t="n"/>
@@ -3623,7 +3305,6 @@
       <c r="C35" s="16" t="n"/>
       <c r="D35" s="16" t="n"/>
       <c r="E35" s="16" t="n"/>
-      <c r="F35" s="16" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="16" t="n"/>
@@ -3631,7 +3312,6 @@
       <c r="C36" s="16" t="n"/>
       <c r="D36" s="16" t="n"/>
       <c r="E36" s="16" t="n"/>
-      <c r="F36" s="16" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="16" t="n"/>
@@ -3639,7 +3319,6 @@
       <c r="C37" s="16" t="n"/>
       <c r="D37" s="16" t="n"/>
       <c r="E37" s="16" t="n"/>
-      <c r="F37" s="16" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="16" t="n"/>
@@ -3647,7 +3326,6 @@
       <c r="C38" s="16" t="n"/>
       <c r="D38" s="16" t="n"/>
       <c r="E38" s="16" t="n"/>
-      <c r="F38" s="16" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="16" t="n"/>
@@ -3655,7 +3333,6 @@
       <c r="C39" s="16" t="n"/>
       <c r="D39" s="16" t="n"/>
       <c r="E39" s="16" t="n"/>
-      <c r="F39" s="16" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="16" t="n"/>
@@ -3663,7 +3340,6 @@
       <c r="C40" s="16" t="n"/>
       <c r="D40" s="16" t="n"/>
       <c r="E40" s="16" t="n"/>
-      <c r="F40" s="16" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="16" t="n"/>
@@ -3671,7 +3347,6 @@
       <c r="C41" s="16" t="n"/>
       <c r="D41" s="16" t="n"/>
       <c r="E41" s="16" t="n"/>
-      <c r="F41" s="16" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="16" t="n"/>
@@ -3679,7 +3354,6 @@
       <c r="C42" s="16" t="n"/>
       <c r="D42" s="16" t="n"/>
       <c r="E42" s="16" t="n"/>
-      <c r="F42" s="16" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="16" t="n"/>
@@ -3687,7 +3361,6 @@
       <c r="C43" s="16" t="n"/>
       <c r="D43" s="16" t="n"/>
       <c r="E43" s="16" t="n"/>
-      <c r="F43" s="16" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="16" t="n"/>
@@ -3695,7 +3368,6 @@
       <c r="C44" s="16" t="n"/>
       <c r="D44" s="16" t="n"/>
       <c r="E44" s="16" t="n"/>
-      <c r="F44" s="16" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="16" t="n"/>
@@ -3703,7 +3375,6 @@
       <c r="C45" s="16" t="n"/>
       <c r="D45" s="16" t="n"/>
       <c r="E45" s="16" t="n"/>
-      <c r="F45" s="16" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="16" t="n"/>
@@ -3711,7 +3382,6 @@
       <c r="C46" s="16" t="n"/>
       <c r="D46" s="16" t="n"/>
       <c r="E46" s="16" t="n"/>
-      <c r="F46" s="16" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="16" t="n"/>
@@ -3719,7 +3389,6 @@
       <c r="C47" s="16" t="n"/>
       <c r="D47" s="16" t="n"/>
       <c r="E47" s="16" t="n"/>
-      <c r="F47" s="16" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="16" t="n"/>
@@ -3727,7 +3396,6 @@
       <c r="C48" s="16" t="n"/>
       <c r="D48" s="16" t="n"/>
       <c r="E48" s="16" t="n"/>
-      <c r="F48" s="16" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="16" t="n"/>
@@ -3735,7 +3403,6 @@
       <c r="C49" s="16" t="n"/>
       <c r="D49" s="16" t="n"/>
       <c r="E49" s="16" t="n"/>
-      <c r="F49" s="16" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="16" t="n"/>
@@ -3743,7 +3410,6 @@
       <c r="C50" s="16" t="n"/>
       <c r="D50" s="16" t="n"/>
       <c r="E50" s="16" t="n"/>
-      <c r="F50" s="16" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="16" t="n"/>
@@ -3751,7 +3417,6 @@
       <c r="C51" s="16" t="n"/>
       <c r="D51" s="16" t="n"/>
       <c r="E51" s="16" t="n"/>
-      <c r="F51" s="16" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="16" t="n"/>
@@ -3759,7 +3424,6 @@
       <c r="C52" s="16" t="n"/>
       <c r="D52" s="16" t="n"/>
       <c r="E52" s="16" t="n"/>
-      <c r="F52" s="16" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="16" t="n"/>
@@ -3767,7 +3431,6 @@
       <c r="C53" s="16" t="n"/>
       <c r="D53" s="16" t="n"/>
       <c r="E53" s="16" t="n"/>
-      <c r="F53" s="16" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="16" t="n"/>
@@ -3775,7 +3438,6 @@
       <c r="C54" s="16" t="n"/>
       <c r="D54" s="16" t="n"/>
       <c r="E54" s="16" t="n"/>
-      <c r="F54" s="16" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="16" t="n"/>
@@ -3783,7 +3445,6 @@
       <c r="C55" s="16" t="n"/>
       <c r="D55" s="16" t="n"/>
       <c r="E55" s="16" t="n"/>
-      <c r="F55" s="16" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="16" t="n"/>
@@ -3791,7 +3452,6 @@
       <c r="C56" s="16" t="n"/>
       <c r="D56" s="16" t="n"/>
       <c r="E56" s="16" t="n"/>
-      <c r="F56" s="16" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="16" t="n"/>
@@ -3799,7 +3459,6 @@
       <c r="C57" s="16" t="n"/>
       <c r="D57" s="16" t="n"/>
       <c r="E57" s="16" t="n"/>
-      <c r="F57" s="16" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="16" t="n"/>
@@ -3807,7 +3466,6 @@
       <c r="C58" s="16" t="n"/>
       <c r="D58" s="16" t="n"/>
       <c r="E58" s="16" t="n"/>
-      <c r="F58" s="16" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="16" t="n"/>
@@ -3815,7 +3473,6 @@
       <c r="C59" s="16" t="n"/>
       <c r="D59" s="16" t="n"/>
       <c r="E59" s="16" t="n"/>
-      <c r="F59" s="16" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="16" t="n"/>
@@ -3823,7 +3480,6 @@
       <c r="C60" s="16" t="n"/>
       <c r="D60" s="16" t="n"/>
       <c r="E60" s="16" t="n"/>
-      <c r="F60" s="16" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="16" t="n"/>
@@ -3831,7 +3487,6 @@
       <c r="C61" s="16" t="n"/>
       <c r="D61" s="16" t="n"/>
       <c r="E61" s="16" t="n"/>
-      <c r="F61" s="16" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="16" t="n"/>
@@ -3839,7 +3494,6 @@
       <c r="C62" s="16" t="n"/>
       <c r="D62" s="16" t="n"/>
       <c r="E62" s="16" t="n"/>
-      <c r="F62" s="16" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="16" t="n"/>
@@ -3847,7 +3501,6 @@
       <c r="C63" s="16" t="n"/>
       <c r="D63" s="16" t="n"/>
       <c r="E63" s="16" t="n"/>
-      <c r="F63" s="16" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="16" t="n"/>
@@ -3855,7 +3508,6 @@
       <c r="C64" s="16" t="n"/>
       <c r="D64" s="16" t="n"/>
       <c r="E64" s="16" t="n"/>
-      <c r="F64" s="16" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="16" t="n"/>
@@ -3863,7 +3515,6 @@
       <c r="C65" s="16" t="n"/>
       <c r="D65" s="16" t="n"/>
       <c r="E65" s="16" t="n"/>
-      <c r="F65" s="16" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="16" t="n"/>
@@ -3871,7 +3522,6 @@
       <c r="C66" s="16" t="n"/>
       <c r="D66" s="16" t="n"/>
       <c r="E66" s="16" t="n"/>
-      <c r="F66" s="16" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="16" t="n"/>
@@ -3879,7 +3529,6 @@
       <c r="C67" s="16" t="n"/>
       <c r="D67" s="16" t="n"/>
       <c r="E67" s="16" t="n"/>
-      <c r="F67" s="16" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="16" t="n"/>
@@ -3887,7 +3536,6 @@
       <c r="C68" s="16" t="n"/>
       <c r="D68" s="16" t="n"/>
       <c r="E68" s="16" t="n"/>
-      <c r="F68" s="16" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="16" t="n"/>
@@ -3895,7 +3543,6 @@
       <c r="C69" s="16" t="n"/>
       <c r="D69" s="16" t="n"/>
       <c r="E69" s="16" t="n"/>
-      <c r="F69" s="16" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="16" t="n"/>
@@ -3903,7 +3550,6 @@
       <c r="C70" s="16" t="n"/>
       <c r="D70" s="16" t="n"/>
       <c r="E70" s="16" t="n"/>
-      <c r="F70" s="16" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="16" t="n"/>
@@ -3911,7 +3557,6 @@
       <c r="C71" s="16" t="n"/>
       <c r="D71" s="16" t="n"/>
       <c r="E71" s="16" t="n"/>
-      <c r="F71" s="16" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="16" t="n"/>
@@ -3919,7 +3564,6 @@
       <c r="C72" s="16" t="n"/>
       <c r="D72" s="16" t="n"/>
       <c r="E72" s="16" t="n"/>
-      <c r="F72" s="16" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="16" t="n"/>
@@ -3927,7 +3571,6 @@
       <c r="C73" s="16" t="n"/>
       <c r="D73" s="16" t="n"/>
       <c r="E73" s="16" t="n"/>
-      <c r="F73" s="16" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="16" t="n"/>
@@ -3935,7 +3578,6 @@
       <c r="C74" s="16" t="n"/>
       <c r="D74" s="16" t="n"/>
       <c r="E74" s="16" t="n"/>
-      <c r="F74" s="16" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="16" t="n"/>
@@ -3943,7 +3585,6 @@
       <c r="C75" s="16" t="n"/>
       <c r="D75" s="16" t="n"/>
       <c r="E75" s="16" t="n"/>
-      <c r="F75" s="16" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="16" t="n"/>
@@ -3951,7 +3592,6 @@
       <c r="C76" s="16" t="n"/>
       <c r="D76" s="16" t="n"/>
       <c r="E76" s="16" t="n"/>
-      <c r="F76" s="16" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="16" t="n"/>
@@ -3959,7 +3599,6 @@
       <c r="C77" s="16" t="n"/>
       <c r="D77" s="16" t="n"/>
       <c r="E77" s="16" t="n"/>
-      <c r="F77" s="16" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="16" t="n"/>
@@ -3967,7 +3606,6 @@
       <c r="C78" s="16" t="n"/>
       <c r="D78" s="16" t="n"/>
       <c r="E78" s="16" t="n"/>
-      <c r="F78" s="16" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="16" t="n"/>
@@ -3975,7 +3613,6 @@
       <c r="C79" s="16" t="n"/>
       <c r="D79" s="16" t="n"/>
       <c r="E79" s="16" t="n"/>
-      <c r="F79" s="16" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="16" t="n"/>
@@ -3983,7 +3620,6 @@
       <c r="C80" s="16" t="n"/>
       <c r="D80" s="16" t="n"/>
       <c r="E80" s="16" t="n"/>
-      <c r="F80" s="16" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="16" t="n"/>
@@ -3991,7 +3627,6 @@
       <c r="C81" s="16" t="n"/>
       <c r="D81" s="16" t="n"/>
       <c r="E81" s="16" t="n"/>
-      <c r="F81" s="16" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="16" t="n"/>
@@ -3999,7 +3634,6 @@
       <c r="C82" s="16" t="n"/>
       <c r="D82" s="16" t="n"/>
       <c r="E82" s="16" t="n"/>
-      <c r="F82" s="16" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="16" t="n"/>
@@ -4007,7 +3641,6 @@
       <c r="C83" s="16" t="n"/>
       <c r="D83" s="16" t="n"/>
       <c r="E83" s="16" t="n"/>
-      <c r="F83" s="16" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="16" t="n"/>
@@ -4015,7 +3648,6 @@
       <c r="C84" s="16" t="n"/>
       <c r="D84" s="16" t="n"/>
       <c r="E84" s="16" t="n"/>
-      <c r="F84" s="16" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="16" t="n"/>
@@ -4023,7 +3655,6 @@
       <c r="C85" s="16" t="n"/>
       <c r="D85" s="16" t="n"/>
       <c r="E85" s="16" t="n"/>
-      <c r="F85" s="16" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="16" t="n"/>
@@ -4031,7 +3662,6 @@
       <c r="C86" s="16" t="n"/>
       <c r="D86" s="16" t="n"/>
       <c r="E86" s="16" t="n"/>
-      <c r="F86" s="16" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="16" t="n"/>
@@ -4039,7 +3669,6 @@
       <c r="C87" s="16" t="n"/>
       <c r="D87" s="16" t="n"/>
       <c r="E87" s="16" t="n"/>
-      <c r="F87" s="16" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="16" t="n"/>
@@ -4047,7 +3676,6 @@
       <c r="C88" s="16" t="n"/>
       <c r="D88" s="16" t="n"/>
       <c r="E88" s="16" t="n"/>
-      <c r="F88" s="16" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n"/>
@@ -4055,7 +3683,6 @@
       <c r="C89" s="7" t="n"/>
       <c r="D89" s="7" t="n"/>
       <c r="E89" s="7" t="n"/>
-      <c r="F89" s="7" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n"/>
@@ -4063,7 +3690,6 @@
       <c r="C90" s="7" t="n"/>
       <c r="D90" s="7" t="n"/>
       <c r="E90" s="7" t="n"/>
-      <c r="F90" s="7" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n"/>
@@ -4071,7 +3697,6 @@
       <c r="C91" s="7" t="n"/>
       <c r="D91" s="7" t="n"/>
       <c r="E91" s="7" t="n"/>
-      <c r="F91" s="7" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n"/>
@@ -4079,7 +3704,6 @@
       <c r="C92" s="7" t="n"/>
       <c r="D92" s="7" t="n"/>
       <c r="E92" s="7" t="n"/>
-      <c r="F92" s="7" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="7" t="n"/>
@@ -4087,7 +3711,6 @@
       <c r="C93" s="7" t="n"/>
       <c r="D93" s="7" t="n"/>
       <c r="E93" s="7" t="n"/>
-      <c r="F93" s="7" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n"/>
@@ -4095,7 +3718,6 @@
       <c r="C94" s="7" t="n"/>
       <c r="D94" s="7" t="n"/>
       <c r="E94" s="7" t="n"/>
-      <c r="F94" s="7" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="7" t="n"/>
@@ -4103,7 +3725,6 @@
       <c r="C95" s="7" t="n"/>
       <c r="D95" s="7" t="n"/>
       <c r="E95" s="7" t="n"/>
-      <c r="F95" s="7" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n"/>
@@ -4111,7 +3732,6 @@
       <c r="C96" s="7" t="n"/>
       <c r="D96" s="7" t="n"/>
       <c r="E96" s="7" t="n"/>
-      <c r="F96" s="7" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="7" t="n"/>
@@ -4119,7 +3739,6 @@
       <c r="C97" s="7" t="n"/>
       <c r="D97" s="7" t="n"/>
       <c r="E97" s="7" t="n"/>
-      <c r="F97" s="7" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n"/>
@@ -4127,7 +3746,6 @@
       <c r="C98" s="7" t="n"/>
       <c r="D98" s="7" t="n"/>
       <c r="E98" s="7" t="n"/>
-      <c r="F98" s="7" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="7" t="n"/>
@@ -4135,7 +3753,6 @@
       <c r="C99" s="7" t="n"/>
       <c r="D99" s="7" t="n"/>
       <c r="E99" s="7" t="n"/>
-      <c r="F99" s="7" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n"/>
@@ -4143,7 +3760,6 @@
       <c r="C100" s="7" t="n"/>
       <c r="D100" s="7" t="n"/>
       <c r="E100" s="7" t="n"/>
-      <c r="F100" s="7" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="7" t="n"/>
@@ -4151,7 +3767,6 @@
       <c r="C101" s="7" t="n"/>
       <c r="D101" s="7" t="n"/>
       <c r="E101" s="7" t="n"/>
-      <c r="F101" s="7" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="7" t="n"/>
@@ -4159,7 +3774,6 @@
       <c r="C102" s="7" t="n"/>
       <c r="D102" s="7" t="n"/>
       <c r="E102" s="7" t="n"/>
-      <c r="F102" s="7" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="7" t="n"/>
@@ -4167,7 +3781,6 @@
       <c r="C103" s="7" t="n"/>
       <c r="D103" s="7" t="n"/>
       <c r="E103" s="7" t="n"/>
-      <c r="F103" s="7" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="7" t="n"/>
@@ -4175,7 +3788,6 @@
       <c r="C104" s="7" t="n"/>
       <c r="D104" s="7" t="n"/>
       <c r="E104" s="7" t="n"/>
-      <c r="F104" s="7" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="7" t="n"/>
@@ -4183,7 +3795,6 @@
       <c r="C105" s="7" t="n"/>
       <c r="D105" s="7" t="n"/>
       <c r="E105" s="7" t="n"/>
-      <c r="F105" s="7" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="7" t="n"/>
@@ -4191,7 +3802,6 @@
       <c r="C106" s="7" t="n"/>
       <c r="D106" s="7" t="n"/>
       <c r="E106" s="7" t="n"/>
-      <c r="F106" s="7" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="7" t="n"/>
@@ -4199,7 +3809,6 @@
       <c r="C107" s="7" t="n"/>
       <c r="D107" s="7" t="n"/>
       <c r="E107" s="7" t="n"/>
-      <c r="F107" s="7" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="7" t="n"/>
@@ -4207,7 +3816,6 @@
       <c r="C108" s="7" t="n"/>
       <c r="D108" s="7" t="n"/>
       <c r="E108" s="7" t="n"/>
-      <c r="F108" s="7" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="7" t="n"/>
@@ -4215,7 +3823,6 @@
       <c r="C109" s="7" t="n"/>
       <c r="D109" s="7" t="n"/>
       <c r="E109" s="7" t="n"/>
-      <c r="F109" s="7" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="7" t="n"/>
@@ -4223,7 +3830,6 @@
       <c r="C110" s="7" t="n"/>
       <c r="D110" s="7" t="n"/>
       <c r="E110" s="7" t="n"/>
-      <c r="F110" s="7" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="7" t="n"/>
@@ -4231,7 +3837,6 @@
       <c r="C111" s="7" t="n"/>
       <c r="D111" s="7" t="n"/>
       <c r="E111" s="7" t="n"/>
-      <c r="F111" s="7" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="7" t="n"/>
@@ -4239,7 +3844,6 @@
       <c r="C112" s="7" t="n"/>
       <c r="D112" s="7" t="n"/>
       <c r="E112" s="7" t="n"/>
-      <c r="F112" s="7" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="7" t="n"/>
@@ -4247,7 +3851,6 @@
       <c r="C113" s="7" t="n"/>
       <c r="D113" s="7" t="n"/>
       <c r="E113" s="7" t="n"/>
-      <c r="F113" s="7" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="7" t="n"/>
@@ -4255,7 +3858,6 @@
       <c r="C114" s="7" t="n"/>
       <c r="D114" s="7" t="n"/>
       <c r="E114" s="7" t="n"/>
-      <c r="F114" s="7" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="7" t="n"/>
@@ -4263,7 +3865,6 @@
       <c r="C115" s="7" t="n"/>
       <c r="D115" s="7" t="n"/>
       <c r="E115" s="7" t="n"/>
-      <c r="F115" s="7" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="7" t="n"/>
@@ -4271,7 +3872,6 @@
       <c r="C116" s="7" t="n"/>
       <c r="D116" s="7" t="n"/>
       <c r="E116" s="7" t="n"/>
-      <c r="F116" s="7" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="7" t="n"/>
@@ -4279,7 +3879,6 @@
       <c r="C117" s="7" t="n"/>
       <c r="D117" s="7" t="n"/>
       <c r="E117" s="7" t="n"/>
-      <c r="F117" s="7" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="7" t="n"/>
@@ -4287,7 +3886,6 @@
       <c r="C118" s="7" t="n"/>
       <c r="D118" s="7" t="n"/>
       <c r="E118" s="7" t="n"/>
-      <c r="F118" s="7" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="7" t="n"/>
@@ -4295,7 +3893,6 @@
       <c r="C119" s="7" t="n"/>
       <c r="D119" s="7" t="n"/>
       <c r="E119" s="7" t="n"/>
-      <c r="F119" s="7" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="7" t="n"/>
@@ -4303,7 +3900,6 @@
       <c r="C120" s="7" t="n"/>
       <c r="D120" s="7" t="n"/>
       <c r="E120" s="7" t="n"/>
-      <c r="F120" s="7" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="7" t="n"/>
@@ -4311,7 +3907,6 @@
       <c r="C121" s="7" t="n"/>
       <c r="D121" s="7" t="n"/>
       <c r="E121" s="7" t="n"/>
-      <c r="F121" s="7" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="7" t="n"/>
@@ -4319,7 +3914,6 @@
       <c r="C122" s="7" t="n"/>
       <c r="D122" s="7" t="n"/>
       <c r="E122" s="7" t="n"/>
-      <c r="F122" s="7" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="7" t="n"/>
@@ -4327,7 +3921,6 @@
       <c r="C123" s="7" t="n"/>
       <c r="D123" s="7" t="n"/>
       <c r="E123" s="7" t="n"/>
-      <c r="F123" s="7" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="7" t="n"/>
@@ -4335,7 +3928,6 @@
       <c r="C124" s="7" t="n"/>
       <c r="D124" s="7" t="n"/>
       <c r="E124" s="7" t="n"/>
-      <c r="F124" s="7" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="7" t="n"/>
@@ -4343,7 +3935,6 @@
       <c r="C125" s="7" t="n"/>
       <c r="D125" s="7" t="n"/>
       <c r="E125" s="7" t="n"/>
-      <c r="F125" s="7" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="7" t="n"/>
@@ -4351,7 +3942,6 @@
       <c r="C126" s="7" t="n"/>
       <c r="D126" s="7" t="n"/>
       <c r="E126" s="7" t="n"/>
-      <c r="F126" s="7" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="7" t="n"/>
@@ -4359,7 +3949,6 @@
       <c r="C127" s="7" t="n"/>
       <c r="D127" s="7" t="n"/>
       <c r="E127" s="7" t="n"/>
-      <c r="F127" s="7" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="7" t="n"/>
@@ -4367,7 +3956,6 @@
       <c r="C128" s="7" t="n"/>
       <c r="D128" s="7" t="n"/>
       <c r="E128" s="7" t="n"/>
-      <c r="F128" s="7" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="7" t="n"/>
@@ -4375,7 +3963,6 @@
       <c r="C129" s="7" t="n"/>
       <c r="D129" s="7" t="n"/>
       <c r="E129" s="7" t="n"/>
-      <c r="F129" s="7" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="7" t="n"/>
@@ -4383,7 +3970,6 @@
       <c r="C130" s="7" t="n"/>
       <c r="D130" s="7" t="n"/>
       <c r="E130" s="7" t="n"/>
-      <c r="F130" s="7" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="7" t="n"/>
@@ -4391,7 +3977,6 @@
       <c r="C131" s="7" t="n"/>
       <c r="D131" s="7" t="n"/>
       <c r="E131" s="7" t="n"/>
-      <c r="F131" s="7" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="7" t="n"/>
@@ -4399,7 +3984,6 @@
       <c r="C132" s="7" t="n"/>
       <c r="D132" s="7" t="n"/>
       <c r="E132" s="7" t="n"/>
-      <c r="F132" s="7" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="7" t="n"/>
@@ -4407,7 +3991,6 @@
       <c r="C133" s="7" t="n"/>
       <c r="D133" s="7" t="n"/>
       <c r="E133" s="7" t="n"/>
-      <c r="F133" s="7" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="7" t="n"/>
@@ -4415,7 +3998,6 @@
       <c r="C134" s="7" t="n"/>
       <c r="D134" s="7" t="n"/>
       <c r="E134" s="7" t="n"/>
-      <c r="F134" s="7" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="7" t="n"/>
@@ -4423,7 +4005,6 @@
       <c r="C135" s="7" t="n"/>
       <c r="D135" s="7" t="n"/>
       <c r="E135" s="7" t="n"/>
-      <c r="F135" s="7" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="7" t="n"/>
@@ -4431,7 +4012,6 @@
       <c r="C136" s="7" t="n"/>
       <c r="D136" s="7" t="n"/>
       <c r="E136" s="7" t="n"/>
-      <c r="F136" s="7" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="7" t="n"/>
@@ -4439,7 +4019,6 @@
       <c r="C137" s="7" t="n"/>
       <c r="D137" s="7" t="n"/>
       <c r="E137" s="7" t="n"/>
-      <c r="F137" s="7" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="7" t="n"/>
@@ -4447,7 +4026,6 @@
       <c r="C138" s="7" t="n"/>
       <c r="D138" s="7" t="n"/>
       <c r="E138" s="7" t="n"/>
-      <c r="F138" s="7" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="7" t="n"/>
@@ -4455,7 +4033,6 @@
       <c r="C139" s="7" t="n"/>
       <c r="D139" s="7" t="n"/>
       <c r="E139" s="7" t="n"/>
-      <c r="F139" s="7" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="7" t="n"/>
@@ -4463,7 +4040,6 @@
       <c r="C140" s="7" t="n"/>
       <c r="D140" s="7" t="n"/>
       <c r="E140" s="7" t="n"/>
-      <c r="F140" s="7" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="7" t="n"/>
@@ -4471,7 +4047,6 @@
       <c r="C141" s="7" t="n"/>
       <c r="D141" s="7" t="n"/>
       <c r="E141" s="7" t="n"/>
-      <c r="F141" s="7" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="7" t="n"/>
@@ -4479,7 +4054,6 @@
       <c r="C142" s="7" t="n"/>
       <c r="D142" s="7" t="n"/>
       <c r="E142" s="7" t="n"/>
-      <c r="F142" s="7" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="7" t="n"/>
@@ -4487,7 +4061,6 @@
       <c r="C143" s="7" t="n"/>
       <c r="D143" s="7" t="n"/>
       <c r="E143" s="7" t="n"/>
-      <c r="F143" s="7" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="7" t="n"/>
@@ -4495,7 +4068,6 @@
       <c r="C144" s="7" t="n"/>
       <c r="D144" s="7" t="n"/>
       <c r="E144" s="7" t="n"/>
-      <c r="F144" s="7" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="7" t="n"/>
@@ -4503,7 +4075,6 @@
       <c r="C145" s="7" t="n"/>
       <c r="D145" s="7" t="n"/>
       <c r="E145" s="7" t="n"/>
-      <c r="F145" s="7" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="7" t="n"/>
@@ -4511,7 +4082,6 @@
       <c r="C146" s="7" t="n"/>
       <c r="D146" s="7" t="n"/>
       <c r="E146" s="7" t="n"/>
-      <c r="F146" s="7" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="7" t="n"/>
@@ -4519,7 +4089,6 @@
       <c r="C147" s="7" t="n"/>
       <c r="D147" s="7" t="n"/>
       <c r="E147" s="7" t="n"/>
-      <c r="F147" s="7" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="7" t="n"/>
@@ -4527,7 +4096,6 @@
       <c r="C148" s="7" t="n"/>
       <c r="D148" s="7" t="n"/>
       <c r="E148" s="7" t="n"/>
-      <c r="F148" s="7" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="7" t="n"/>
@@ -4535,7 +4103,6 @@
       <c r="C149" s="7" t="n"/>
       <c r="D149" s="7" t="n"/>
       <c r="E149" s="7" t="n"/>
-      <c r="F149" s="7" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="7" t="n"/>
@@ -4543,7 +4110,6 @@
       <c r="C150" s="7" t="n"/>
       <c r="D150" s="7" t="n"/>
       <c r="E150" s="7" t="n"/>
-      <c r="F150" s="7" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="7" t="n"/>
@@ -4551,7 +4117,6 @@
       <c r="C151" s="7" t="n"/>
       <c r="D151" s="7" t="n"/>
       <c r="E151" s="7" t="n"/>
-      <c r="F151" s="7" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="7" t="n"/>
@@ -4559,7 +4124,6 @@
       <c r="C152" s="7" t="n"/>
       <c r="D152" s="7" t="n"/>
       <c r="E152" s="7" t="n"/>
-      <c r="F152" s="7" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="7" t="n"/>
@@ -4567,7 +4131,6 @@
       <c r="C153" s="7" t="n"/>
       <c r="D153" s="7" t="n"/>
       <c r="E153" s="7" t="n"/>
-      <c r="F153" s="7" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="7" t="n"/>
@@ -4575,7 +4138,6 @@
       <c r="C154" s="7" t="n"/>
       <c r="D154" s="7" t="n"/>
       <c r="E154" s="7" t="n"/>
-      <c r="F154" s="7" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="7" t="n"/>
@@ -4583,7 +4145,6 @@
       <c r="C155" s="7" t="n"/>
       <c r="D155" s="7" t="n"/>
       <c r="E155" s="7" t="n"/>
-      <c r="F155" s="7" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="7" t="n"/>
@@ -4591,7 +4152,6 @@
       <c r="C156" s="7" t="n"/>
       <c r="D156" s="7" t="n"/>
       <c r="E156" s="7" t="n"/>
-      <c r="F156" s="7" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="7" t="n"/>
@@ -4599,7 +4159,6 @@
       <c r="C157" s="7" t="n"/>
       <c r="D157" s="7" t="n"/>
       <c r="E157" s="7" t="n"/>
-      <c r="F157" s="7" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="7" t="n"/>
@@ -4607,7 +4166,6 @@
       <c r="C158" s="7" t="n"/>
       <c r="D158" s="7" t="n"/>
       <c r="E158" s="7" t="n"/>
-      <c r="F158" s="7" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="7" t="n"/>
@@ -4615,7 +4173,6 @@
       <c r="C159" s="7" t="n"/>
       <c r="D159" s="7" t="n"/>
       <c r="E159" s="7" t="n"/>
-      <c r="F159" s="7" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="7" t="n"/>
@@ -4623,7 +4180,6 @@
       <c r="C160" s="7" t="n"/>
       <c r="D160" s="7" t="n"/>
       <c r="E160" s="7" t="n"/>
-      <c r="F160" s="7" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="7" t="n"/>
@@ -4631,7 +4187,6 @@
       <c r="C161" s="7" t="n"/>
       <c r="D161" s="7" t="n"/>
       <c r="E161" s="7" t="n"/>
-      <c r="F161" s="7" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="7" t="n"/>
@@ -4639,7 +4194,6 @@
       <c r="C162" s="7" t="n"/>
       <c r="D162" s="7" t="n"/>
       <c r="E162" s="7" t="n"/>
-      <c r="F162" s="7" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="7" t="n"/>
@@ -4647,7 +4201,6 @@
       <c r="C163" s="7" t="n"/>
       <c r="D163" s="7" t="n"/>
       <c r="E163" s="7" t="n"/>
-      <c r="F163" s="7" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="7" t="n"/>
@@ -4655,7 +4208,6 @@
       <c r="C164" s="7" t="n"/>
       <c r="D164" s="7" t="n"/>
       <c r="E164" s="7" t="n"/>
-      <c r="F164" s="7" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="7" t="n"/>
@@ -4663,7 +4215,6 @@
       <c r="C165" s="7" t="n"/>
       <c r="D165" s="7" t="n"/>
       <c r="E165" s="7" t="n"/>
-      <c r="F165" s="7" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="7" t="n"/>
@@ -4671,7 +4222,6 @@
       <c r="C166" s="7" t="n"/>
       <c r="D166" s="7" t="n"/>
       <c r="E166" s="7" t="n"/>
-      <c r="F166" s="7" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="7" t="n"/>
@@ -4679,7 +4229,6 @@
       <c r="C167" s="7" t="n"/>
       <c r="D167" s="7" t="n"/>
       <c r="E167" s="7" t="n"/>
-      <c r="F167" s="7" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="7" t="n"/>
@@ -4687,7 +4236,6 @@
       <c r="C168" s="7" t="n"/>
       <c r="D168" s="7" t="n"/>
       <c r="E168" s="7" t="n"/>
-      <c r="F168" s="7" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="7" t="n"/>
@@ -4695,7 +4243,6 @@
       <c r="C169" s="7" t="n"/>
       <c r="D169" s="7" t="n"/>
       <c r="E169" s="7" t="n"/>
-      <c r="F169" s="7" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="7" t="n"/>
@@ -4703,7 +4250,6 @@
       <c r="C170" s="7" t="n"/>
       <c r="D170" s="7" t="n"/>
       <c r="E170" s="7" t="n"/>
-      <c r="F170" s="7" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="7" t="n"/>
@@ -4711,7 +4257,6 @@
       <c r="C171" s="7" t="n"/>
       <c r="D171" s="7" t="n"/>
       <c r="E171" s="7" t="n"/>
-      <c r="F171" s="7" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="7" t="n"/>
@@ -4719,7 +4264,6 @@
       <c r="C172" s="7" t="n"/>
       <c r="D172" s="7" t="n"/>
       <c r="E172" s="7" t="n"/>
-      <c r="F172" s="7" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="7" t="n"/>
@@ -4727,7 +4271,6 @@
       <c r="C173" s="7" t="n"/>
       <c r="D173" s="7" t="n"/>
       <c r="E173" s="7" t="n"/>
-      <c r="F173" s="7" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="7" t="n"/>
@@ -4735,7 +4278,6 @@
       <c r="C174" s="7" t="n"/>
       <c r="D174" s="7" t="n"/>
       <c r="E174" s="7" t="n"/>
-      <c r="F174" s="7" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="7" t="n"/>
@@ -4743,7 +4285,6 @@
       <c r="C175" s="7" t="n"/>
       <c r="D175" s="7" t="n"/>
       <c r="E175" s="7" t="n"/>
-      <c r="F175" s="7" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="7" t="n"/>
@@ -4751,7 +4292,6 @@
       <c r="C176" s="7" t="n"/>
       <c r="D176" s="7" t="n"/>
       <c r="E176" s="7" t="n"/>
-      <c r="F176" s="7" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="7" t="n"/>
@@ -4759,7 +4299,6 @@
       <c r="C177" s="7" t="n"/>
       <c r="D177" s="7" t="n"/>
       <c r="E177" s="7" t="n"/>
-      <c r="F177" s="7" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="7" t="n"/>
@@ -4767,7 +4306,6 @@
       <c r="C178" s="7" t="n"/>
       <c r="D178" s="7" t="n"/>
       <c r="E178" s="7" t="n"/>
-      <c r="F178" s="7" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="7" t="n"/>
@@ -4775,7 +4313,6 @@
       <c r="C179" s="7" t="n"/>
       <c r="D179" s="7" t="n"/>
       <c r="E179" s="7" t="n"/>
-      <c r="F179" s="7" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="7" t="n"/>
@@ -4783,7 +4320,6 @@
       <c r="C180" s="7" t="n"/>
       <c r="D180" s="7" t="n"/>
       <c r="E180" s="7" t="n"/>
-      <c r="F180" s="7" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="7" t="n"/>
@@ -4791,7 +4327,6 @@
       <c r="C181" s="7" t="n"/>
       <c r="D181" s="7" t="n"/>
       <c r="E181" s="7" t="n"/>
-      <c r="F181" s="7" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="7" t="n"/>
@@ -4799,7 +4334,6 @@
       <c r="C182" s="7" t="n"/>
       <c r="D182" s="7" t="n"/>
       <c r="E182" s="7" t="n"/>
-      <c r="F182" s="7" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="7" t="n"/>
@@ -4807,7 +4341,6 @@
       <c r="C183" s="7" t="n"/>
       <c r="D183" s="7" t="n"/>
       <c r="E183" s="7" t="n"/>
-      <c r="F183" s="7" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="7" t="n"/>
@@ -4815,7 +4348,6 @@
       <c r="C184" s="7" t="n"/>
       <c r="D184" s="7" t="n"/>
       <c r="E184" s="7" t="n"/>
-      <c r="F184" s="7" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="7" t="n"/>
@@ -4823,7 +4355,6 @@
       <c r="C185" s="7" t="n"/>
       <c r="D185" s="7" t="n"/>
       <c r="E185" s="7" t="n"/>
-      <c r="F185" s="7" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="7" t="n"/>
@@ -4831,7 +4362,6 @@
       <c r="C186" s="7" t="n"/>
       <c r="D186" s="7" t="n"/>
       <c r="E186" s="7" t="n"/>
-      <c r="F186" s="7" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="7" t="n"/>
@@ -4839,7 +4369,6 @@
       <c r="C187" s="7" t="n"/>
       <c r="D187" s="7" t="n"/>
       <c r="E187" s="7" t="n"/>
-      <c r="F187" s="7" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="7" t="n"/>
@@ -4847,7 +4376,6 @@
       <c r="C188" s="7" t="n"/>
       <c r="D188" s="7" t="n"/>
       <c r="E188" s="7" t="n"/>
-      <c r="F188" s="7" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="7" t="n"/>
@@ -4855,7 +4383,6 @@
       <c r="C189" s="7" t="n"/>
       <c r="D189" s="7" t="n"/>
       <c r="E189" s="7" t="n"/>
-      <c r="F189" s="7" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="7" t="n"/>
@@ -4863,7 +4390,6 @@
       <c r="C190" s="7" t="n"/>
       <c r="D190" s="7" t="n"/>
       <c r="E190" s="7" t="n"/>
-      <c r="F190" s="7" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="7" t="n"/>
@@ -4871,7 +4397,6 @@
       <c r="C191" s="7" t="n"/>
       <c r="D191" s="7" t="n"/>
       <c r="E191" s="7" t="n"/>
-      <c r="F191" s="7" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="7" t="n"/>
@@ -4879,7 +4404,6 @@
       <c r="C192" s="7" t="n"/>
       <c r="D192" s="7" t="n"/>
       <c r="E192" s="7" t="n"/>
-      <c r="F192" s="7" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="7" t="n"/>
@@ -4887,7 +4411,6 @@
       <c r="C193" s="7" t="n"/>
       <c r="D193" s="7" t="n"/>
       <c r="E193" s="7" t="n"/>
-      <c r="F193" s="7" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="7" t="n"/>
@@ -4895,7 +4418,6 @@
       <c r="C194" s="7" t="n"/>
       <c r="D194" s="7" t="n"/>
       <c r="E194" s="7" t="n"/>
-      <c r="F194" s="7" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="7" t="n"/>
@@ -4903,7 +4425,6 @@
       <c r="C195" s="7" t="n"/>
       <c r="D195" s="7" t="n"/>
       <c r="E195" s="7" t="n"/>
-      <c r="F195" s="7" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="7" t="n"/>
@@ -4911,7 +4432,6 @@
       <c r="C196" s="7" t="n"/>
       <c r="D196" s="7" t="n"/>
       <c r="E196" s="7" t="n"/>
-      <c r="F196" s="7" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="7" t="n"/>
@@ -4919,7 +4439,6 @@
       <c r="C197" s="7" t="n"/>
       <c r="D197" s="7" t="n"/>
       <c r="E197" s="7" t="n"/>
-      <c r="F197" s="7" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="7" t="n"/>
@@ -4927,7 +4446,6 @@
       <c r="C198" s="7" t="n"/>
       <c r="D198" s="7" t="n"/>
       <c r="E198" s="7" t="n"/>
-      <c r="F198" s="7" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="7" t="n"/>
@@ -4935,7 +4453,6 @@
       <c r="C199" s="7" t="n"/>
       <c r="D199" s="7" t="n"/>
       <c r="E199" s="7" t="n"/>
-      <c r="F199" s="7" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="7" t="n"/>
@@ -4943,7 +4460,6 @@
       <c r="C200" s="7" t="n"/>
       <c r="D200" s="7" t="n"/>
       <c r="E200" s="7" t="n"/>
-      <c r="F200" s="7" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="7" t="n"/>
@@ -4951,7 +4467,6 @@
       <c r="C201" s="7" t="n"/>
       <c r="D201" s="7" t="n"/>
       <c r="E201" s="7" t="n"/>
-      <c r="F201" s="7" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="7" t="n"/>
@@ -4959,7 +4474,6 @@
       <c r="C202" s="7" t="n"/>
       <c r="D202" s="7" t="n"/>
       <c r="E202" s="7" t="n"/>
-      <c r="F202" s="7" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="7" t="n"/>
@@ -4967,7 +4481,6 @@
       <c r="C203" s="7" t="n"/>
       <c r="D203" s="7" t="n"/>
       <c r="E203" s="7" t="n"/>
-      <c r="F203" s="7" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="7" t="n"/>
@@ -4975,7 +4488,6 @@
       <c r="C204" s="7" t="n"/>
       <c r="D204" s="7" t="n"/>
       <c r="E204" s="7" t="n"/>
-      <c r="F204" s="7" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="7" t="n"/>
@@ -4983,7 +4495,6 @@
       <c r="C205" s="7" t="n"/>
       <c r="D205" s="7" t="n"/>
       <c r="E205" s="7" t="n"/>
-      <c r="F205" s="7" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="7" t="n"/>
@@ -4991,7 +4502,6 @@
       <c r="C206" s="7" t="n"/>
       <c r="D206" s="7" t="n"/>
       <c r="E206" s="7" t="n"/>
-      <c r="F206" s="7" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="7" t="n"/>
@@ -4999,7 +4509,6 @@
       <c r="C207" s="7" t="n"/>
       <c r="D207" s="7" t="n"/>
       <c r="E207" s="7" t="n"/>
-      <c r="F207" s="7" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="7" t="n"/>
@@ -5007,7 +4516,6 @@
       <c r="C208" s="7" t="n"/>
       <c r="D208" s="7" t="n"/>
       <c r="E208" s="7" t="n"/>
-      <c r="F208" s="7" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="7" t="n"/>
@@ -5015,7 +4523,6 @@
       <c r="C209" s="7" t="n"/>
       <c r="D209" s="7" t="n"/>
       <c r="E209" s="7" t="n"/>
-      <c r="F209" s="7" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="7" t="n"/>
@@ -5023,7 +4530,6 @@
       <c r="C210" s="7" t="n"/>
       <c r="D210" s="7" t="n"/>
       <c r="E210" s="7" t="n"/>
-      <c r="F210" s="7" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="7" t="n"/>
@@ -5031,7 +4537,6 @@
       <c r="C211" s="7" t="n"/>
       <c r="D211" s="7" t="n"/>
       <c r="E211" s="7" t="n"/>
-      <c r="F211" s="7" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="7" t="n"/>
@@ -5039,7 +4544,6 @@
       <c r="C212" s="7" t="n"/>
       <c r="D212" s="7" t="n"/>
       <c r="E212" s="7" t="n"/>
-      <c r="F212" s="7" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="7" t="n"/>
@@ -5047,7 +4551,6 @@
       <c r="C213" s="7" t="n"/>
       <c r="D213" s="7" t="n"/>
       <c r="E213" s="7" t="n"/>
-      <c r="F213" s="7" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="7" t="n"/>
@@ -5055,7 +4558,6 @@
       <c r="C214" s="7" t="n"/>
       <c r="D214" s="7" t="n"/>
       <c r="E214" s="7" t="n"/>
-      <c r="F214" s="7" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="7" t="n"/>
@@ -5063,7 +4565,6 @@
       <c r="C215" s="7" t="n"/>
       <c r="D215" s="7" t="n"/>
       <c r="E215" s="7" t="n"/>
-      <c r="F215" s="7" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="7" t="n"/>
@@ -5071,7 +4572,6 @@
       <c r="C216" s="7" t="n"/>
       <c r="D216" s="7" t="n"/>
       <c r="E216" s="7" t="n"/>
-      <c r="F216" s="7" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="7" t="n"/>
@@ -5079,7 +4579,6 @@
       <c r="C217" s="7" t="n"/>
       <c r="D217" s="7" t="n"/>
       <c r="E217" s="7" t="n"/>
-      <c r="F217" s="7" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="7" t="n"/>
@@ -5087,7 +4586,6 @@
       <c r="C218" s="7" t="n"/>
       <c r="D218" s="7" t="n"/>
       <c r="E218" s="7" t="n"/>
-      <c r="F218" s="7" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="7" t="n"/>
@@ -5095,7 +4593,6 @@
       <c r="C219" s="7" t="n"/>
       <c r="D219" s="7" t="n"/>
       <c r="E219" s="7" t="n"/>
-      <c r="F219" s="7" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="7" t="n"/>
@@ -5103,7 +4600,6 @@
       <c r="C220" s="7" t="n"/>
       <c r="D220" s="7" t="n"/>
       <c r="E220" s="7" t="n"/>
-      <c r="F220" s="7" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="7" t="n"/>
@@ -5111,7 +4607,6 @@
       <c r="C221" s="7" t="n"/>
       <c r="D221" s="7" t="n"/>
       <c r="E221" s="7" t="n"/>
-      <c r="F221" s="7" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="7" t="n"/>
@@ -5119,7 +4614,6 @@
       <c r="C222" s="7" t="n"/>
       <c r="D222" s="7" t="n"/>
       <c r="E222" s="7" t="n"/>
-      <c r="F222" s="7" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="7" t="n"/>
@@ -5127,7 +4621,6 @@
       <c r="C223" s="7" t="n"/>
       <c r="D223" s="7" t="n"/>
       <c r="E223" s="7" t="n"/>
-      <c r="F223" s="7" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="7" t="n"/>
@@ -5135,7 +4628,6 @@
       <c r="C224" s="7" t="n"/>
       <c r="D224" s="7" t="n"/>
       <c r="E224" s="7" t="n"/>
-      <c r="F224" s="7" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="7" t="n"/>
@@ -5143,7 +4635,6 @@
       <c r="C225" s="7" t="n"/>
       <c r="D225" s="7" t="n"/>
       <c r="E225" s="7" t="n"/>
-      <c r="F225" s="7" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="7" t="n"/>
@@ -5151,7 +4642,6 @@
       <c r="C226" s="7" t="n"/>
       <c r="D226" s="7" t="n"/>
       <c r="E226" s="7" t="n"/>
-      <c r="F226" s="7" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="7" t="n"/>
@@ -5159,7 +4649,6 @@
       <c r="C227" s="7" t="n"/>
       <c r="D227" s="7" t="n"/>
       <c r="E227" s="7" t="n"/>
-      <c r="F227" s="7" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="7" t="n"/>
@@ -5167,7 +4656,6 @@
       <c r="C228" s="7" t="n"/>
       <c r="D228" s="7" t="n"/>
       <c r="E228" s="7" t="n"/>
-      <c r="F228" s="7" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="7" t="n"/>
@@ -5175,7 +4663,6 @@
       <c r="C229" s="7" t="n"/>
       <c r="D229" s="7" t="n"/>
       <c r="E229" s="7" t="n"/>
-      <c r="F229" s="7" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="7" t="n"/>
@@ -5183,7 +4670,6 @@
       <c r="C230" s="7" t="n"/>
       <c r="D230" s="7" t="n"/>
       <c r="E230" s="7" t="n"/>
-      <c r="F230" s="7" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="7" t="n"/>
@@ -5191,7 +4677,6 @@
       <c r="C231" s="7" t="n"/>
       <c r="D231" s="7" t="n"/>
       <c r="E231" s="7" t="n"/>
-      <c r="F231" s="7" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="7" t="n"/>
@@ -5199,7 +4684,6 @@
       <c r="C232" s="7" t="n"/>
       <c r="D232" s="7" t="n"/>
       <c r="E232" s="7" t="n"/>
-      <c r="F232" s="7" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="7" t="n"/>
@@ -5207,7 +4691,6 @@
       <c r="C233" s="7" t="n"/>
       <c r="D233" s="7" t="n"/>
       <c r="E233" s="7" t="n"/>
-      <c r="F233" s="7" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="7" t="n"/>
@@ -5215,7 +4698,6 @@
       <c r="C234" s="7" t="n"/>
       <c r="D234" s="7" t="n"/>
       <c r="E234" s="7" t="n"/>
-      <c r="F234" s="7" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="7" t="n"/>
@@ -5223,7 +4705,6 @@
       <c r="C235" s="7" t="n"/>
       <c r="D235" s="7" t="n"/>
       <c r="E235" s="7" t="n"/>
-      <c r="F235" s="7" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="7" t="n"/>
@@ -5231,7 +4712,6 @@
       <c r="C236" s="7" t="n"/>
       <c r="D236" s="7" t="n"/>
       <c r="E236" s="7" t="n"/>
-      <c r="F236" s="7" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="7" t="n"/>
@@ -5239,7 +4719,6 @@
       <c r="C237" s="7" t="n"/>
       <c r="D237" s="7" t="n"/>
       <c r="E237" s="7" t="n"/>
-      <c r="F237" s="7" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="7" t="n"/>
@@ -5247,7 +4726,6 @@
       <c r="C238" s="7" t="n"/>
       <c r="D238" s="7" t="n"/>
       <c r="E238" s="7" t="n"/>
-      <c r="F238" s="7" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="7" t="n"/>
@@ -5255,7 +4733,6 @@
       <c r="C239" s="7" t="n"/>
       <c r="D239" s="7" t="n"/>
       <c r="E239" s="7" t="n"/>
-      <c r="F239" s="7" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="7" t="n"/>
@@ -5263,7 +4740,6 @@
       <c r="C240" s="7" t="n"/>
       <c r="D240" s="7" t="n"/>
       <c r="E240" s="7" t="n"/>
-      <c r="F240" s="7" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="7" t="n"/>
@@ -5271,7 +4747,6 @@
       <c r="C241" s="7" t="n"/>
       <c r="D241" s="7" t="n"/>
       <c r="E241" s="7" t="n"/>
-      <c r="F241" s="7" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="7" t="n"/>
@@ -5279,7 +4754,6 @@
       <c r="C242" s="7" t="n"/>
       <c r="D242" s="7" t="n"/>
       <c r="E242" s="7" t="n"/>
-      <c r="F242" s="7" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="7" t="n"/>
@@ -5287,7 +4761,6 @@
       <c r="C243" s="7" t="n"/>
       <c r="D243" s="7" t="n"/>
       <c r="E243" s="7" t="n"/>
-      <c r="F243" s="7" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="7" t="n"/>
@@ -5295,7 +4768,6 @@
       <c r="C244" s="7" t="n"/>
       <c r="D244" s="7" t="n"/>
       <c r="E244" s="7" t="n"/>
-      <c r="F244" s="7" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="7" t="n"/>
@@ -5303,7 +4775,6 @@
       <c r="C245" s="7" t="n"/>
       <c r="D245" s="7" t="n"/>
       <c r="E245" s="7" t="n"/>
-      <c r="F245" s="7" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="7" t="n"/>
@@ -5311,7 +4782,6 @@
       <c r="C246" s="7" t="n"/>
       <c r="D246" s="7" t="n"/>
       <c r="E246" s="7" t="n"/>
-      <c r="F246" s="7" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="7" t="n"/>
@@ -5319,7 +4789,6 @@
       <c r="C247" s="7" t="n"/>
       <c r="D247" s="7" t="n"/>
       <c r="E247" s="7" t="n"/>
-      <c r="F247" s="7" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="7" t="n"/>
@@ -5327,7 +4796,6 @@
       <c r="C248" s="7" t="n"/>
       <c r="D248" s="7" t="n"/>
       <c r="E248" s="7" t="n"/>
-      <c r="F248" s="7" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="7" t="n"/>
@@ -5335,7 +4803,6 @@
       <c r="C249" s="7" t="n"/>
       <c r="D249" s="7" t="n"/>
       <c r="E249" s="7" t="n"/>
-      <c r="F249" s="7" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="7" t="n"/>
@@ -5343,7 +4810,6 @@
       <c r="C250" s="7" t="n"/>
       <c r="D250" s="7" t="n"/>
       <c r="E250" s="7" t="n"/>
-      <c r="F250" s="7" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="7" t="n"/>
@@ -5351,7 +4817,6 @@
       <c r="C251" s="7" t="n"/>
       <c r="D251" s="7" t="n"/>
       <c r="E251" s="7" t="n"/>
-      <c r="F251" s="7" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="7" t="n"/>
@@ -5359,7 +4824,6 @@
       <c r="C252" s="7" t="n"/>
       <c r="D252" s="7" t="n"/>
       <c r="E252" s="7" t="n"/>
-      <c r="F252" s="7" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="7" t="n"/>
@@ -5367,7 +4831,6 @@
       <c r="C253" s="7" t="n"/>
       <c r="D253" s="7" t="n"/>
       <c r="E253" s="7" t="n"/>
-      <c r="F253" s="7" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="7" t="n"/>
@@ -5375,7 +4838,6 @@
       <c r="C254" s="7" t="n"/>
       <c r="D254" s="7" t="n"/>
       <c r="E254" s="7" t="n"/>
-      <c r="F254" s="7" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="7" t="n"/>
@@ -5383,7 +4845,6 @@
       <c r="C255" s="7" t="n"/>
       <c r="D255" s="7" t="n"/>
       <c r="E255" s="7" t="n"/>
-      <c r="F255" s="7" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="7" t="n"/>
@@ -5391,7 +4852,6 @@
       <c r="C256" s="7" t="n"/>
       <c r="D256" s="7" t="n"/>
       <c r="E256" s="7" t="n"/>
-      <c r="F256" s="7" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="7" t="n"/>
@@ -5399,7 +4859,6 @@
       <c r="C257" s="7" t="n"/>
       <c r="D257" s="7" t="n"/>
       <c r="E257" s="7" t="n"/>
-      <c r="F257" s="7" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="7" t="n"/>
@@ -5407,7 +4866,6 @@
       <c r="C258" s="7" t="n"/>
       <c r="D258" s="7" t="n"/>
       <c r="E258" s="7" t="n"/>
-      <c r="F258" s="7" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="7" t="n"/>
@@ -5415,7 +4873,6 @@
       <c r="C259" s="7" t="n"/>
       <c r="D259" s="7" t="n"/>
       <c r="E259" s="7" t="n"/>
-      <c r="F259" s="7" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="7" t="n"/>
@@ -5423,7 +4880,6 @@
       <c r="C260" s="7" t="n"/>
       <c r="D260" s="7" t="n"/>
       <c r="E260" s="7" t="n"/>
-      <c r="F260" s="7" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="7" t="n"/>
@@ -5431,7 +4887,6 @@
       <c r="C261" s="7" t="n"/>
       <c r="D261" s="7" t="n"/>
       <c r="E261" s="7" t="n"/>
-      <c r="F261" s="7" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="7" t="n"/>
@@ -5439,7 +4894,6 @@
       <c r="C262" s="7" t="n"/>
       <c r="D262" s="7" t="n"/>
       <c r="E262" s="7" t="n"/>
-      <c r="F262" s="7" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="7" t="n"/>
@@ -5447,7 +4901,6 @@
       <c r="C263" s="7" t="n"/>
       <c r="D263" s="7" t="n"/>
       <c r="E263" s="7" t="n"/>
-      <c r="F263" s="7" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="7" t="n"/>
@@ -5455,7 +4908,6 @@
       <c r="C264" s="7" t="n"/>
       <c r="D264" s="7" t="n"/>
       <c r="E264" s="7" t="n"/>
-      <c r="F264" s="7" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="7" t="n"/>
@@ -5463,7 +4915,6 @@
       <c r="C265" s="7" t="n"/>
       <c r="D265" s="7" t="n"/>
       <c r="E265" s="7" t="n"/>
-      <c r="F265" s="7" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="7" t="n"/>
@@ -5471,7 +4922,6 @@
       <c r="C266" s="7" t="n"/>
       <c r="D266" s="7" t="n"/>
       <c r="E266" s="7" t="n"/>
-      <c r="F266" s="7" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="7" t="n"/>
@@ -5479,7 +4929,6 @@
       <c r="C267" s="7" t="n"/>
       <c r="D267" s="7" t="n"/>
       <c r="E267" s="7" t="n"/>
-      <c r="F267" s="7" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="7" t="n"/>
@@ -5487,7 +4936,6 @@
       <c r="C268" s="7" t="n"/>
       <c r="D268" s="7" t="n"/>
       <c r="E268" s="7" t="n"/>
-      <c r="F268" s="7" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="7" t="n"/>
@@ -5495,7 +4943,6 @@
       <c r="C269" s="7" t="n"/>
       <c r="D269" s="7" t="n"/>
       <c r="E269" s="7" t="n"/>
-      <c r="F269" s="7" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="7" t="n"/>
@@ -5503,7 +4950,6 @@
       <c r="C270" s="7" t="n"/>
       <c r="D270" s="7" t="n"/>
       <c r="E270" s="7" t="n"/>
-      <c r="F270" s="7" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="7" t="n"/>
@@ -5511,7 +4957,6 @@
       <c r="C271" s="7" t="n"/>
       <c r="D271" s="7" t="n"/>
       <c r="E271" s="7" t="n"/>
-      <c r="F271" s="7" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="7" t="n"/>
@@ -5519,7 +4964,6 @@
       <c r="C272" s="7" t="n"/>
       <c r="D272" s="7" t="n"/>
       <c r="E272" s="7" t="n"/>
-      <c r="F272" s="7" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="7" t="n"/>
@@ -5527,7 +4971,6 @@
       <c r="C273" s="7" t="n"/>
       <c r="D273" s="7" t="n"/>
       <c r="E273" s="7" t="n"/>
-      <c r="F273" s="7" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="7" t="n"/>
@@ -5535,7 +4978,6 @@
       <c r="C274" s="7" t="n"/>
       <c r="D274" s="7" t="n"/>
       <c r="E274" s="7" t="n"/>
-      <c r="F274" s="7" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="7" t="n"/>
@@ -5543,7 +4985,6 @@
       <c r="C275" s="7" t="n"/>
       <c r="D275" s="7" t="n"/>
       <c r="E275" s="7" t="n"/>
-      <c r="F275" s="7" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="7" t="n"/>
@@ -5551,7 +4992,6 @@
       <c r="C276" s="7" t="n"/>
       <c r="D276" s="7" t="n"/>
       <c r="E276" s="7" t="n"/>
-      <c r="F276" s="7" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="7" t="n"/>
@@ -5559,7 +4999,6 @@
       <c r="C277" s="7" t="n"/>
       <c r="D277" s="7" t="n"/>
       <c r="E277" s="7" t="n"/>
-      <c r="F277" s="7" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="7" t="n"/>
@@ -5567,7 +5006,6 @@
       <c r="C278" s="7" t="n"/>
       <c r="D278" s="7" t="n"/>
       <c r="E278" s="7" t="n"/>
-      <c r="F278" s="7" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="7" t="n"/>
@@ -5575,7 +5013,6 @@
       <c r="C279" s="7" t="n"/>
       <c r="D279" s="7" t="n"/>
       <c r="E279" s="7" t="n"/>
-      <c r="F279" s="7" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="7" t="n"/>
@@ -5583,7 +5020,6 @@
       <c r="C280" s="7" t="n"/>
       <c r="D280" s="7" t="n"/>
       <c r="E280" s="7" t="n"/>
-      <c r="F280" s="7" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="7" t="n"/>
@@ -5591,7 +5027,6 @@
       <c r="C281" s="7" t="n"/>
       <c r="D281" s="7" t="n"/>
       <c r="E281" s="7" t="n"/>
-      <c r="F281" s="7" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="7" t="n"/>
@@ -5599,7 +5034,6 @@
       <c r="C282" s="7" t="n"/>
       <c r="D282" s="7" t="n"/>
       <c r="E282" s="7" t="n"/>
-      <c r="F282" s="7" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="7" t="n"/>
@@ -5607,7 +5041,6 @@
       <c r="C283" s="7" t="n"/>
       <c r="D283" s="7" t="n"/>
       <c r="E283" s="7" t="n"/>
-      <c r="F283" s="7" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="7" t="n"/>
@@ -5615,7 +5048,6 @@
       <c r="C284" s="7" t="n"/>
       <c r="D284" s="7" t="n"/>
       <c r="E284" s="7" t="n"/>
-      <c r="F284" s="7" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="7" t="n"/>
@@ -5623,7 +5055,6 @@
       <c r="C285" s="7" t="n"/>
       <c r="D285" s="7" t="n"/>
       <c r="E285" s="7" t="n"/>
-      <c r="F285" s="7" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="7" t="n"/>
@@ -5631,7 +5062,6 @@
       <c r="C286" s="7" t="n"/>
       <c r="D286" s="7" t="n"/>
       <c r="E286" s="7" t="n"/>
-      <c r="F286" s="7" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="7" t="n"/>
@@ -5639,7 +5069,6 @@
       <c r="C287" s="7" t="n"/>
       <c r="D287" s="7" t="n"/>
       <c r="E287" s="7" t="n"/>
-      <c r="F287" s="7" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="7" t="n"/>
@@ -5647,7 +5076,6 @@
       <c r="C288" s="7" t="n"/>
       <c r="D288" s="7" t="n"/>
       <c r="E288" s="7" t="n"/>
-      <c r="F288" s="7" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="7" t="n"/>
@@ -5655,7 +5083,6 @@
       <c r="C289" s="7" t="n"/>
       <c r="D289" s="7" t="n"/>
       <c r="E289" s="7" t="n"/>
-      <c r="F289" s="7" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="7" t="n"/>
@@ -5663,7 +5090,6 @@
       <c r="C290" s="7" t="n"/>
       <c r="D290" s="7" t="n"/>
       <c r="E290" s="7" t="n"/>
-      <c r="F290" s="7" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="7" t="n"/>
@@ -5671,7 +5097,6 @@
       <c r="C291" s="7" t="n"/>
       <c r="D291" s="7" t="n"/>
       <c r="E291" s="7" t="n"/>
-      <c r="F291" s="7" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="7" t="n"/>
@@ -5679,7 +5104,6 @@
       <c r="C292" s="7" t="n"/>
       <c r="D292" s="7" t="n"/>
       <c r="E292" s="7" t="n"/>
-      <c r="F292" s="7" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="7" t="n"/>
@@ -5687,7 +5111,6 @@
       <c r="C293" s="7" t="n"/>
       <c r="D293" s="7" t="n"/>
       <c r="E293" s="7" t="n"/>
-      <c r="F293" s="7" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="7" t="n"/>
@@ -5695,7 +5118,6 @@
       <c r="C294" s="7" t="n"/>
       <c r="D294" s="7" t="n"/>
       <c r="E294" s="7" t="n"/>
-      <c r="F294" s="7" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="7" t="n"/>
@@ -5703,7 +5125,6 @@
       <c r="C295" s="7" t="n"/>
       <c r="D295" s="7" t="n"/>
       <c r="E295" s="7" t="n"/>
-      <c r="F295" s="7" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="7" t="n"/>
@@ -5711,7 +5132,6 @@
       <c r="C296" s="7" t="n"/>
       <c r="D296" s="7" t="n"/>
       <c r="E296" s="7" t="n"/>
-      <c r="F296" s="7" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="7" t="n"/>
@@ -5719,7 +5139,6 @@
       <c r="C297" s="7" t="n"/>
       <c r="D297" s="7" t="n"/>
       <c r="E297" s="7" t="n"/>
-      <c r="F297" s="7" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="7" t="n"/>
@@ -5727,7 +5146,6 @@
       <c r="C298" s="7" t="n"/>
       <c r="D298" s="7" t="n"/>
       <c r="E298" s="7" t="n"/>
-      <c r="F298" s="7" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="7" t="n"/>
@@ -5735,7 +5153,6 @@
       <c r="C299" s="7" t="n"/>
       <c r="D299" s="7" t="n"/>
       <c r="E299" s="7" t="n"/>
-      <c r="F299" s="7" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="7" t="n"/>
@@ -5743,7 +5160,6 @@
       <c r="C300" s="7" t="n"/>
       <c r="D300" s="7" t="n"/>
       <c r="E300" s="7" t="n"/>
-      <c r="F300" s="7" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="7" t="n"/>
@@ -5751,7 +5167,6 @@
       <c r="C301" s="7" t="n"/>
       <c r="D301" s="7" t="n"/>
       <c r="E301" s="7" t="n"/>
-      <c r="F301" s="7" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="7" t="n"/>
@@ -5759,7 +5174,6 @@
       <c r="C302" s="7" t="n"/>
       <c r="D302" s="7" t="n"/>
       <c r="E302" s="7" t="n"/>
-      <c r="F302" s="7" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="7" t="n"/>
@@ -5767,7 +5181,6 @@
       <c r="C303" s="7" t="n"/>
       <c r="D303" s="7" t="n"/>
       <c r="E303" s="7" t="n"/>
-      <c r="F303" s="7" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="7" t="n"/>
@@ -5775,7 +5188,6 @@
       <c r="C304" s="7" t="n"/>
       <c r="D304" s="7" t="n"/>
       <c r="E304" s="7" t="n"/>
-      <c r="F304" s="7" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="7" t="n"/>
@@ -5783,7 +5195,6 @@
       <c r="C305" s="7" t="n"/>
       <c r="D305" s="7" t="n"/>
       <c r="E305" s="7" t="n"/>
-      <c r="F305" s="7" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="7" t="n"/>
@@ -5791,7 +5202,6 @@
       <c r="C306" s="7" t="n"/>
       <c r="D306" s="7" t="n"/>
       <c r="E306" s="7" t="n"/>
-      <c r="F306" s="7" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="7" t="n"/>
@@ -5799,7 +5209,6 @@
       <c r="C307" s="7" t="n"/>
       <c r="D307" s="7" t="n"/>
       <c r="E307" s="7" t="n"/>
-      <c r="F307" s="7" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="7" t="n"/>
@@ -5807,7 +5216,6 @@
       <c r="C308" s="7" t="n"/>
       <c r="D308" s="7" t="n"/>
       <c r="E308" s="7" t="n"/>
-      <c r="F308" s="7" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="7" t="n"/>
@@ -5815,7 +5223,6 @@
       <c r="C309" s="7" t="n"/>
       <c r="D309" s="7" t="n"/>
       <c r="E309" s="7" t="n"/>
-      <c r="F309" s="7" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="7" t="n"/>
@@ -5823,7 +5230,6 @@
       <c r="C310" s="7" t="n"/>
       <c r="D310" s="7" t="n"/>
       <c r="E310" s="7" t="n"/>
-      <c r="F310" s="7" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="7" t="n"/>
@@ -5831,7 +5237,6 @@
       <c r="C311" s="7" t="n"/>
       <c r="D311" s="7" t="n"/>
       <c r="E311" s="7" t="n"/>
-      <c r="F311" s="7" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="7" t="n"/>
@@ -5839,7 +5244,6 @@
       <c r="C312" s="7" t="n"/>
       <c r="D312" s="7" t="n"/>
       <c r="E312" s="7" t="n"/>
-      <c r="F312" s="7" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="7" t="n"/>
@@ -5847,7 +5251,6 @@
       <c r="C313" s="7" t="n"/>
       <c r="D313" s="7" t="n"/>
       <c r="E313" s="7" t="n"/>
-      <c r="F313" s="7" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="7" t="n"/>
@@ -5855,7 +5258,6 @@
       <c r="C314" s="7" t="n"/>
       <c r="D314" s="7" t="n"/>
       <c r="E314" s="7" t="n"/>
-      <c r="F314" s="7" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="7" t="n"/>
@@ -5863,7 +5265,6 @@
       <c r="C315" s="7" t="n"/>
       <c r="D315" s="7" t="n"/>
       <c r="E315" s="7" t="n"/>
-      <c r="F315" s="7" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="7" t="n"/>
@@ -5871,7 +5272,6 @@
       <c r="C316" s="7" t="n"/>
       <c r="D316" s="7" t="n"/>
       <c r="E316" s="7" t="n"/>
-      <c r="F316" s="7" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="7" t="n"/>
@@ -5879,7 +5279,6 @@
       <c r="C317" s="7" t="n"/>
       <c r="D317" s="7" t="n"/>
       <c r="E317" s="7" t="n"/>
-      <c r="F317" s="7" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="7" t="n"/>
@@ -5887,7 +5286,6 @@
       <c r="C318" s="7" t="n"/>
       <c r="D318" s="7" t="n"/>
       <c r="E318" s="7" t="n"/>
-      <c r="F318" s="7" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="7" t="n"/>
@@ -5895,7 +5293,6 @@
       <c r="C319" s="7" t="n"/>
       <c r="D319" s="7" t="n"/>
       <c r="E319" s="7" t="n"/>
-      <c r="F319" s="7" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="7" t="n"/>
@@ -5903,7 +5300,6 @@
       <c r="C320" s="7" t="n"/>
       <c r="D320" s="7" t="n"/>
       <c r="E320" s="7" t="n"/>
-      <c r="F320" s="7" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="7" t="n"/>
@@ -5911,7 +5307,6 @@
       <c r="C321" s="7" t="n"/>
       <c r="D321" s="7" t="n"/>
       <c r="E321" s="7" t="n"/>
-      <c r="F321" s="7" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="7" t="n"/>
@@ -5919,7 +5314,6 @@
       <c r="C322" s="7" t="n"/>
       <c r="D322" s="7" t="n"/>
       <c r="E322" s="7" t="n"/>
-      <c r="F322" s="7" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="7" t="n"/>
@@ -5927,7 +5321,6 @@
       <c r="C323" s="7" t="n"/>
       <c r="D323" s="7" t="n"/>
       <c r="E323" s="7" t="n"/>
-      <c r="F323" s="7" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="7" t="n"/>
@@ -5935,7 +5328,6 @@
       <c r="C324" s="7" t="n"/>
       <c r="D324" s="7" t="n"/>
       <c r="E324" s="7" t="n"/>
-      <c r="F324" s="7" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="7" t="n"/>
@@ -5943,7 +5335,6 @@
       <c r="C325" s="7" t="n"/>
       <c r="D325" s="7" t="n"/>
       <c r="E325" s="7" t="n"/>
-      <c r="F325" s="7" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="7" t="n"/>
@@ -5951,7 +5342,6 @@
       <c r="C326" s="7" t="n"/>
       <c r="D326" s="7" t="n"/>
       <c r="E326" s="7" t="n"/>
-      <c r="F326" s="7" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="7" t="n"/>
@@ -5959,7 +5349,6 @@
       <c r="C327" s="7" t="n"/>
       <c r="D327" s="7" t="n"/>
       <c r="E327" s="7" t="n"/>
-      <c r="F327" s="7" t="n"/>
     </row>
     <row r="328">
       <c r="A328" s="7" t="n"/>
@@ -5967,7 +5356,6 @@
       <c r="C328" s="7" t="n"/>
       <c r="D328" s="7" t="n"/>
       <c r="E328" s="7" t="n"/>
-      <c r="F328" s="7" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="7" t="n"/>
@@ -5975,7 +5363,6 @@
       <c r="C329" s="7" t="n"/>
       <c r="D329" s="7" t="n"/>
       <c r="E329" s="7" t="n"/>
-      <c r="F329" s="7" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="7" t="n"/>
@@ -5983,7 +5370,6 @@
       <c r="C330" s="7" t="n"/>
       <c r="D330" s="7" t="n"/>
       <c r="E330" s="7" t="n"/>
-      <c r="F330" s="7" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="7" t="n"/>
@@ -5991,7 +5377,6 @@
       <c r="C331" s="7" t="n"/>
       <c r="D331" s="7" t="n"/>
       <c r="E331" s="7" t="n"/>
-      <c r="F331" s="7" t="n"/>
     </row>
     <row r="332">
       <c r="A332" s="7" t="n"/>
@@ -5999,7 +5384,6 @@
       <c r="C332" s="7" t="n"/>
       <c r="D332" s="7" t="n"/>
       <c r="E332" s="7" t="n"/>
-      <c r="F332" s="7" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="7" t="n"/>
@@ -6007,7 +5391,6 @@
       <c r="C333" s="7" t="n"/>
       <c r="D333" s="7" t="n"/>
       <c r="E333" s="7" t="n"/>
-      <c r="F333" s="7" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="7" t="n"/>
@@ -6015,7 +5398,6 @@
       <c r="C334" s="7" t="n"/>
       <c r="D334" s="7" t="n"/>
       <c r="E334" s="7" t="n"/>
-      <c r="F334" s="7" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="7" t="n"/>
@@ -6023,7 +5405,6 @@
       <c r="C335" s="7" t="n"/>
       <c r="D335" s="7" t="n"/>
       <c r="E335" s="7" t="n"/>
-      <c r="F335" s="7" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="7" t="n"/>
@@ -6031,7 +5412,6 @@
       <c r="C336" s="7" t="n"/>
       <c r="D336" s="7" t="n"/>
       <c r="E336" s="7" t="n"/>
-      <c r="F336" s="7" t="n"/>
     </row>
     <row r="337">
       <c r="A337" s="7" t="n"/>
@@ -6039,7 +5419,6 @@
       <c r="C337" s="7" t="n"/>
       <c r="D337" s="7" t="n"/>
       <c r="E337" s="7" t="n"/>
-      <c r="F337" s="7" t="n"/>
     </row>
     <row r="338">
       <c r="A338" s="7" t="n"/>
@@ -6047,7 +5426,6 @@
       <c r="C338" s="7" t="n"/>
       <c r="D338" s="7" t="n"/>
       <c r="E338" s="7" t="n"/>
-      <c r="F338" s="7" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="7" t="n"/>
@@ -6055,7 +5433,6 @@
       <c r="C339" s="7" t="n"/>
       <c r="D339" s="7" t="n"/>
       <c r="E339" s="7" t="n"/>
-      <c r="F339" s="7" t="n"/>
     </row>
     <row r="340">
       <c r="A340" s="7" t="n"/>
@@ -6063,7 +5440,6 @@
       <c r="C340" s="7" t="n"/>
       <c r="D340" s="7" t="n"/>
       <c r="E340" s="7" t="n"/>
-      <c r="F340" s="7" t="n"/>
     </row>
     <row r="341">
       <c r="A341" s="7" t="n"/>
@@ -6071,7 +5447,6 @@
       <c r="C341" s="7" t="n"/>
       <c r="D341" s="7" t="n"/>
       <c r="E341" s="7" t="n"/>
-      <c r="F341" s="7" t="n"/>
     </row>
     <row r="342">
       <c r="A342" s="7" t="n"/>
@@ -6079,7 +5454,6 @@
       <c r="C342" s="7" t="n"/>
       <c r="D342" s="7" t="n"/>
       <c r="E342" s="7" t="n"/>
-      <c r="F342" s="7" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="7" t="n"/>
@@ -6087,7 +5461,6 @@
       <c r="C343" s="7" t="n"/>
       <c r="D343" s="7" t="n"/>
       <c r="E343" s="7" t="n"/>
-      <c r="F343" s="7" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="7" t="n"/>
@@ -6095,7 +5468,6 @@
       <c r="C344" s="7" t="n"/>
       <c r="D344" s="7" t="n"/>
       <c r="E344" s="7" t="n"/>
-      <c r="F344" s="7" t="n"/>
     </row>
     <row r="345">
       <c r="A345" s="7" t="n"/>
@@ -6103,7 +5475,6 @@
       <c r="C345" s="7" t="n"/>
       <c r="D345" s="7" t="n"/>
       <c r="E345" s="7" t="n"/>
-      <c r="F345" s="7" t="n"/>
     </row>
     <row r="346">
       <c r="A346" s="7" t="n"/>
@@ -6111,7 +5482,6 @@
       <c r="C346" s="7" t="n"/>
       <c r="D346" s="7" t="n"/>
       <c r="E346" s="7" t="n"/>
-      <c r="F346" s="7" t="n"/>
     </row>
     <row r="347">
       <c r="A347" s="7" t="n"/>
@@ -6119,7 +5489,6 @@
       <c r="C347" s="7" t="n"/>
       <c r="D347" s="7" t="n"/>
       <c r="E347" s="7" t="n"/>
-      <c r="F347" s="7" t="n"/>
     </row>
     <row r="348">
       <c r="A348" s="7" t="n"/>
@@ -6127,7 +5496,6 @@
       <c r="C348" s="7" t="n"/>
       <c r="D348" s="7" t="n"/>
       <c r="E348" s="7" t="n"/>
-      <c r="F348" s="7" t="n"/>
     </row>
     <row r="349">
       <c r="A349" s="7" t="n"/>
@@ -6135,7 +5503,6 @@
       <c r="C349" s="7" t="n"/>
       <c r="D349" s="7" t="n"/>
       <c r="E349" s="7" t="n"/>
-      <c r="F349" s="7" t="n"/>
     </row>
     <row r="350">
       <c r="A350" s="7" t="n"/>
@@ -6143,7 +5510,6 @@
       <c r="C350" s="7" t="n"/>
       <c r="D350" s="7" t="n"/>
       <c r="E350" s="7" t="n"/>
-      <c r="F350" s="7" t="n"/>
     </row>
     <row r="351">
       <c r="A351" s="7" t="n"/>
@@ -6151,7 +5517,6 @@
       <c r="C351" s="7" t="n"/>
       <c r="D351" s="7" t="n"/>
       <c r="E351" s="7" t="n"/>
-      <c r="F351" s="7" t="n"/>
     </row>
     <row r="352">
       <c r="A352" s="7" t="n"/>
@@ -6159,7 +5524,6 @@
       <c r="C352" s="7" t="n"/>
       <c r="D352" s="7" t="n"/>
       <c r="E352" s="7" t="n"/>
-      <c r="F352" s="7" t="n"/>
     </row>
     <row r="353">
       <c r="A353" s="7" t="n"/>
@@ -6167,7 +5531,6 @@
       <c r="C353" s="7" t="n"/>
       <c r="D353" s="7" t="n"/>
       <c r="E353" s="7" t="n"/>
-      <c r="F353" s="7" t="n"/>
     </row>
     <row r="354">
       <c r="A354" s="7" t="n"/>
@@ -6175,7 +5538,6 @@
       <c r="C354" s="7" t="n"/>
       <c r="D354" s="7" t="n"/>
       <c r="E354" s="7" t="n"/>
-      <c r="F354" s="7" t="n"/>
     </row>
     <row r="355">
       <c r="A355" s="7" t="n"/>
@@ -6183,7 +5545,6 @@
       <c r="C355" s="7" t="n"/>
       <c r="D355" s="7" t="n"/>
       <c r="E355" s="7" t="n"/>
-      <c r="F355" s="7" t="n"/>
     </row>
     <row r="356">
       <c r="A356" s="7" t="n"/>
@@ -6191,7 +5552,6 @@
       <c r="C356" s="7" t="n"/>
       <c r="D356" s="7" t="n"/>
       <c r="E356" s="7" t="n"/>
-      <c r="F356" s="7" t="n"/>
     </row>
     <row r="357">
       <c r="A357" s="7" t="n"/>
@@ -6199,7 +5559,6 @@
       <c r="C357" s="7" t="n"/>
       <c r="D357" s="7" t="n"/>
       <c r="E357" s="7" t="n"/>
-      <c r="F357" s="7" t="n"/>
     </row>
     <row r="358">
       <c r="A358" s="7" t="n"/>
@@ -6207,7 +5566,6 @@
       <c r="C358" s="7" t="n"/>
       <c r="D358" s="7" t="n"/>
       <c r="E358" s="7" t="n"/>
-      <c r="F358" s="7" t="n"/>
     </row>
     <row r="359">
       <c r="A359" s="7" t="n"/>
@@ -6215,7 +5573,6 @@
       <c r="C359" s="7" t="n"/>
       <c r="D359" s="7" t="n"/>
       <c r="E359" s="7" t="n"/>
-      <c r="F359" s="7" t="n"/>
     </row>
     <row r="360">
       <c r="A360" s="7" t="n"/>
@@ -6223,7 +5580,6 @@
       <c r="C360" s="7" t="n"/>
       <c r="D360" s="7" t="n"/>
       <c r="E360" s="7" t="n"/>
-      <c r="F360" s="7" t="n"/>
     </row>
     <row r="361">
       <c r="A361" s="7" t="n"/>
@@ -6231,7 +5587,6 @@
       <c r="C361" s="7" t="n"/>
       <c r="D361" s="7" t="n"/>
       <c r="E361" s="7" t="n"/>
-      <c r="F361" s="7" t="n"/>
     </row>
     <row r="362">
       <c r="A362" s="7" t="n"/>
@@ -6239,7 +5594,6 @@
       <c r="C362" s="7" t="n"/>
       <c r="D362" s="7" t="n"/>
       <c r="E362" s="7" t="n"/>
-      <c r="F362" s="7" t="n"/>
     </row>
     <row r="363">
       <c r="A363" s="7" t="n"/>
@@ -6247,7 +5601,6 @@
       <c r="C363" s="7" t="n"/>
       <c r="D363" s="7" t="n"/>
       <c r="E363" s="7" t="n"/>
-      <c r="F363" s="7" t="n"/>
     </row>
     <row r="364">
       <c r="A364" s="7" t="n"/>
@@ -6255,7 +5608,6 @@
       <c r="C364" s="7" t="n"/>
       <c r="D364" s="7" t="n"/>
       <c r="E364" s="7" t="n"/>
-      <c r="F364" s="7" t="n"/>
     </row>
     <row r="365">
       <c r="A365" s="7" t="n"/>
@@ -6263,7 +5615,6 @@
       <c r="C365" s="7" t="n"/>
       <c r="D365" s="7" t="n"/>
       <c r="E365" s="7" t="n"/>
-      <c r="F365" s="7" t="n"/>
     </row>
     <row r="366">
       <c r="A366" s="7" t="n"/>
@@ -6271,7 +5622,6 @@
       <c r="C366" s="7" t="n"/>
       <c r="D366" s="7" t="n"/>
       <c r="E366" s="7" t="n"/>
-      <c r="F366" s="7" t="n"/>
     </row>
     <row r="367">
       <c r="A367" s="7" t="n"/>
@@ -6279,7 +5629,6 @@
       <c r="C367" s="7" t="n"/>
       <c r="D367" s="7" t="n"/>
       <c r="E367" s="7" t="n"/>
-      <c r="F367" s="7" t="n"/>
     </row>
     <row r="368">
       <c r="A368" s="7" t="n"/>
@@ -6287,7 +5636,6 @@
       <c r="C368" s="7" t="n"/>
       <c r="D368" s="7" t="n"/>
       <c r="E368" s="7" t="n"/>
-      <c r="F368" s="7" t="n"/>
     </row>
     <row r="369">
       <c r="A369" s="7" t="n"/>
@@ -6295,7 +5643,6 @@
       <c r="C369" s="7" t="n"/>
       <c r="D369" s="7" t="n"/>
       <c r="E369" s="7" t="n"/>
-      <c r="F369" s="7" t="n"/>
     </row>
     <row r="370">
       <c r="A370" s="7" t="n"/>
@@ -6303,7 +5650,6 @@
       <c r="C370" s="7" t="n"/>
       <c r="D370" s="7" t="n"/>
       <c r="E370" s="7" t="n"/>
-      <c r="F370" s="7" t="n"/>
     </row>
     <row r="371">
       <c r="A371" s="7" t="n"/>
@@ -6311,7 +5657,6 @@
       <c r="C371" s="7" t="n"/>
       <c r="D371" s="7" t="n"/>
       <c r="E371" s="7" t="n"/>
-      <c r="F371" s="7" t="n"/>
     </row>
     <row r="372">
       <c r="A372" s="7" t="n"/>
@@ -6319,7 +5664,6 @@
       <c r="C372" s="7" t="n"/>
       <c r="D372" s="7" t="n"/>
       <c r="E372" s="7" t="n"/>
-      <c r="F372" s="7" t="n"/>
     </row>
     <row r="373">
       <c r="A373" s="7" t="n"/>
@@ -6327,7 +5671,6 @@
       <c r="C373" s="7" t="n"/>
       <c r="D373" s="7" t="n"/>
       <c r="E373" s="7" t="n"/>
-      <c r="F373" s="7" t="n"/>
     </row>
     <row r="374">
       <c r="A374" s="7" t="n"/>
@@ -6335,7 +5678,6 @@
       <c r="C374" s="7" t="n"/>
       <c r="D374" s="7" t="n"/>
       <c r="E374" s="7" t="n"/>
-      <c r="F374" s="7" t="n"/>
     </row>
     <row r="375">
       <c r="A375" s="7" t="n"/>
@@ -6343,7 +5685,6 @@
       <c r="C375" s="7" t="n"/>
       <c r="D375" s="7" t="n"/>
       <c r="E375" s="7" t="n"/>
-      <c r="F375" s="7" t="n"/>
     </row>
     <row r="376">
       <c r="A376" s="7" t="n"/>
@@ -6351,7 +5692,6 @@
       <c r="C376" s="7" t="n"/>
       <c r="D376" s="7" t="n"/>
       <c r="E376" s="7" t="n"/>
-      <c r="F376" s="7" t="n"/>
     </row>
     <row r="377">
       <c r="A377" s="7" t="n"/>
@@ -6359,7 +5699,6 @@
       <c r="C377" s="7" t="n"/>
       <c r="D377" s="7" t="n"/>
       <c r="E377" s="7" t="n"/>
-      <c r="F377" s="7" t="n"/>
     </row>
     <row r="378">
       <c r="A378" s="7" t="n"/>
@@ -6367,7 +5706,6 @@
       <c r="C378" s="7" t="n"/>
       <c r="D378" s="7" t="n"/>
       <c r="E378" s="7" t="n"/>
-      <c r="F378" s="7" t="n"/>
     </row>
     <row r="379">
       <c r="A379" s="7" t="n"/>
@@ -6375,7 +5713,6 @@
       <c r="C379" s="7" t="n"/>
       <c r="D379" s="7" t="n"/>
       <c r="E379" s="7" t="n"/>
-      <c r="F379" s="7" t="n"/>
     </row>
     <row r="380">
       <c r="A380" s="7" t="n"/>
@@ -6383,7 +5720,6 @@
       <c r="C380" s="7" t="n"/>
       <c r="D380" s="7" t="n"/>
       <c r="E380" s="7" t="n"/>
-      <c r="F380" s="7" t="n"/>
     </row>
     <row r="381">
       <c r="A381" s="7" t="n"/>
@@ -6391,7 +5727,6 @@
       <c r="C381" s="7" t="n"/>
       <c r="D381" s="7" t="n"/>
       <c r="E381" s="7" t="n"/>
-      <c r="F381" s="7" t="n"/>
     </row>
     <row r="382">
       <c r="A382" s="7" t="n"/>
@@ -6399,7 +5734,6 @@
       <c r="C382" s="7" t="n"/>
       <c r="D382" s="7" t="n"/>
       <c r="E382" s="7" t="n"/>
-      <c r="F382" s="7" t="n"/>
     </row>
     <row r="383">
       <c r="A383" s="7" t="n"/>
@@ -6407,7 +5741,6 @@
       <c r="C383" s="7" t="n"/>
       <c r="D383" s="7" t="n"/>
       <c r="E383" s="7" t="n"/>
-      <c r="F383" s="7" t="n"/>
     </row>
     <row r="384">
       <c r="A384" s="7" t="n"/>
@@ -6415,7 +5748,6 @@
       <c r="C384" s="7" t="n"/>
       <c r="D384" s="7" t="n"/>
       <c r="E384" s="7" t="n"/>
-      <c r="F384" s="7" t="n"/>
     </row>
     <row r="385">
       <c r="A385" s="7" t="n"/>
@@ -6423,7 +5755,6 @@
       <c r="C385" s="7" t="n"/>
       <c r="D385" s="7" t="n"/>
       <c r="E385" s="7" t="n"/>
-      <c r="F385" s="7" t="n"/>
     </row>
     <row r="386">
       <c r="A386" s="7" t="n"/>
@@ -6431,7 +5762,6 @@
       <c r="C386" s="7" t="n"/>
       <c r="D386" s="7" t="n"/>
       <c r="E386" s="7" t="n"/>
-      <c r="F386" s="7" t="n"/>
     </row>
     <row r="387">
       <c r="A387" s="7" t="n"/>
@@ -6439,7 +5769,6 @@
       <c r="C387" s="7" t="n"/>
       <c r="D387" s="7" t="n"/>
       <c r="E387" s="7" t="n"/>
-      <c r="F387" s="7" t="n"/>
     </row>
     <row r="388">
       <c r="A388" s="7" t="n"/>
@@ -6447,7 +5776,6 @@
       <c r="C388" s="7" t="n"/>
       <c r="D388" s="7" t="n"/>
       <c r="E388" s="7" t="n"/>
-      <c r="F388" s="7" t="n"/>
     </row>
     <row r="389">
       <c r="A389" s="7" t="n"/>
@@ -6455,7 +5783,6 @@
       <c r="C389" s="7" t="n"/>
       <c r="D389" s="7" t="n"/>
       <c r="E389" s="7" t="n"/>
-      <c r="F389" s="7" t="n"/>
     </row>
     <row r="390">
       <c r="A390" s="7" t="n"/>
@@ -6463,7 +5790,6 @@
       <c r="C390" s="7" t="n"/>
       <c r="D390" s="7" t="n"/>
       <c r="E390" s="7" t="n"/>
-      <c r="F390" s="7" t="n"/>
     </row>
     <row r="391">
       <c r="A391" s="7" t="n"/>
@@ -6471,7 +5797,6 @@
       <c r="C391" s="7" t="n"/>
       <c r="D391" s="7" t="n"/>
       <c r="E391" s="7" t="n"/>
-      <c r="F391" s="7" t="n"/>
     </row>
     <row r="392">
       <c r="A392" s="7" t="n"/>
@@ -6479,7 +5804,6 @@
       <c r="C392" s="7" t="n"/>
       <c r="D392" s="7" t="n"/>
       <c r="E392" s="7" t="n"/>
-      <c r="F392" s="7" t="n"/>
     </row>
     <row r="393">
       <c r="A393" s="7" t="n"/>
@@ -6487,7 +5811,6 @@
       <c r="C393" s="7" t="n"/>
       <c r="D393" s="7" t="n"/>
       <c r="E393" s="7" t="n"/>
-      <c r="F393" s="7" t="n"/>
     </row>
     <row r="394">
       <c r="A394" s="7" t="n"/>
@@ -6495,7 +5818,6 @@
       <c r="C394" s="7" t="n"/>
       <c r="D394" s="7" t="n"/>
       <c r="E394" s="7" t="n"/>
-      <c r="F394" s="7" t="n"/>
     </row>
     <row r="395">
       <c r="A395" s="7" t="n"/>
@@ -6503,7 +5825,6 @@
       <c r="C395" s="7" t="n"/>
       <c r="D395" s="7" t="n"/>
       <c r="E395" s="7" t="n"/>
-      <c r="F395" s="7" t="n"/>
     </row>
     <row r="396">
       <c r="A396" s="7" t="n"/>
@@ -6511,7 +5832,6 @@
       <c r="C396" s="7" t="n"/>
       <c r="D396" s="7" t="n"/>
       <c r="E396" s="7" t="n"/>
-      <c r="F396" s="7" t="n"/>
     </row>
     <row r="397">
       <c r="A397" s="7" t="n"/>
@@ -6519,7 +5839,6 @@
       <c r="C397" s="7" t="n"/>
       <c r="D397" s="7" t="n"/>
       <c r="E397" s="7" t="n"/>
-      <c r="F397" s="7" t="n"/>
     </row>
     <row r="398">
       <c r="A398" s="7" t="n"/>
@@ -6527,7 +5846,6 @@
       <c r="C398" s="7" t="n"/>
       <c r="D398" s="7" t="n"/>
       <c r="E398" s="7" t="n"/>
-      <c r="F398" s="7" t="n"/>
     </row>
     <row r="399">
       <c r="A399" s="7" t="n"/>
@@ -6535,7 +5853,6 @@
       <c r="C399" s="7" t="n"/>
       <c r="D399" s="7" t="n"/>
       <c r="E399" s="7" t="n"/>
-      <c r="F399" s="7" t="n"/>
     </row>
     <row r="400">
       <c r="A400" s="7" t="n"/>
@@ -6543,7 +5860,6 @@
       <c r="C400" s="7" t="n"/>
       <c r="D400" s="7" t="n"/>
       <c r="E400" s="7" t="n"/>
-      <c r="F400" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6562,13 +5878,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M120"/>
+  <dimension ref="A1:L120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6661,11 +5977,6 @@
           <t>Sam matin</t>
         </is>
       </c>
-      <c r="M3" s="12" t="inlineStr">
-        <is>
-          <t>Précisions (horaires exacts…)</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="16" t="n"/>
@@ -6680,7 +5991,6 @@
       <c r="J4" s="16" t="n"/>
       <c r="K4" s="16" t="n"/>
       <c r="L4" s="16" t="n"/>
-      <c r="M4" s="16" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="16" t="n"/>
@@ -6695,7 +6005,6 @@
       <c r="J5" s="16" t="n"/>
       <c r="K5" s="16" t="n"/>
       <c r="L5" s="16" t="n"/>
-      <c r="M5" s="16" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="16" t="n"/>
@@ -6710,7 +6019,6 @@
       <c r="J6" s="16" t="n"/>
       <c r="K6" s="16" t="n"/>
       <c r="L6" s="16" t="n"/>
-      <c r="M6" s="16" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="16" t="n"/>
@@ -6725,7 +6033,6 @@
       <c r="J7" s="16" t="n"/>
       <c r="K7" s="16" t="n"/>
       <c r="L7" s="16" t="n"/>
-      <c r="M7" s="16" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="16" t="n"/>
@@ -6740,7 +6047,6 @@
       <c r="J8" s="16" t="n"/>
       <c r="K8" s="16" t="n"/>
       <c r="L8" s="16" t="n"/>
-      <c r="M8" s="16" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n"/>
@@ -6755,7 +6061,6 @@
       <c r="J9" s="7" t="n"/>
       <c r="K9" s="7" t="n"/>
       <c r="L9" s="7" t="n"/>
-      <c r="M9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n"/>
@@ -6770,7 +6075,6 @@
       <c r="J10" s="7" t="n"/>
       <c r="K10" s="7" t="n"/>
       <c r="L10" s="7" t="n"/>
-      <c r="M10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n"/>
@@ -6785,7 +6089,6 @@
       <c r="J11" s="7" t="n"/>
       <c r="K11" s="7" t="n"/>
       <c r="L11" s="7" t="n"/>
-      <c r="M11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n"/>
@@ -6800,7 +6103,6 @@
       <c r="J12" s="7" t="n"/>
       <c r="K12" s="7" t="n"/>
       <c r="L12" s="7" t="n"/>
-      <c r="M12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n"/>
@@ -6815,7 +6117,6 @@
       <c r="J13" s="7" t="n"/>
       <c r="K13" s="7" t="n"/>
       <c r="L13" s="7" t="n"/>
-      <c r="M13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n"/>
@@ -6830,7 +6131,6 @@
       <c r="J14" s="7" t="n"/>
       <c r="K14" s="7" t="n"/>
       <c r="L14" s="7" t="n"/>
-      <c r="M14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n"/>
@@ -6845,7 +6145,6 @@
       <c r="J15" s="7" t="n"/>
       <c r="K15" s="7" t="n"/>
       <c r="L15" s="7" t="n"/>
-      <c r="M15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n"/>
@@ -6860,7 +6159,6 @@
       <c r="J16" s="7" t="n"/>
       <c r="K16" s="7" t="n"/>
       <c r="L16" s="7" t="n"/>
-      <c r="M16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n"/>
@@ -6875,7 +6173,6 @@
       <c r="J17" s="7" t="n"/>
       <c r="K17" s="7" t="n"/>
       <c r="L17" s="7" t="n"/>
-      <c r="M17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n"/>
@@ -6890,7 +6187,6 @@
       <c r="J18" s="7" t="n"/>
       <c r="K18" s="7" t="n"/>
       <c r="L18" s="7" t="n"/>
-      <c r="M18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n"/>
@@ -6905,7 +6201,6 @@
       <c r="J19" s="7" t="n"/>
       <c r="K19" s="7" t="n"/>
       <c r="L19" s="7" t="n"/>
-      <c r="M19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n"/>
@@ -6920,7 +6215,6 @@
       <c r="J20" s="7" t="n"/>
       <c r="K20" s="7" t="n"/>
       <c r="L20" s="7" t="n"/>
-      <c r="M20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n"/>
@@ -6935,7 +6229,6 @@
       <c r="J21" s="7" t="n"/>
       <c r="K21" s="7" t="n"/>
       <c r="L21" s="7" t="n"/>
-      <c r="M21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n"/>
@@ -6950,7 +6243,6 @@
       <c r="J22" s="7" t="n"/>
       <c r="K22" s="7" t="n"/>
       <c r="L22" s="7" t="n"/>
-      <c r="M22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n"/>
@@ -6965,7 +6257,6 @@
       <c r="J23" s="7" t="n"/>
       <c r="K23" s="7" t="n"/>
       <c r="L23" s="7" t="n"/>
-      <c r="M23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n"/>
@@ -6980,7 +6271,6 @@
       <c r="J24" s="7" t="n"/>
       <c r="K24" s="7" t="n"/>
       <c r="L24" s="7" t="n"/>
-      <c r="M24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n"/>
@@ -6995,7 +6285,6 @@
       <c r="J25" s="7" t="n"/>
       <c r="K25" s="7" t="n"/>
       <c r="L25" s="7" t="n"/>
-      <c r="M25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n"/>
@@ -7010,7 +6299,6 @@
       <c r="J26" s="7" t="n"/>
       <c r="K26" s="7" t="n"/>
       <c r="L26" s="7" t="n"/>
-      <c r="M26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n"/>
@@ -7025,7 +6313,6 @@
       <c r="J27" s="7" t="n"/>
       <c r="K27" s="7" t="n"/>
       <c r="L27" s="7" t="n"/>
-      <c r="M27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n"/>
@@ -7040,7 +6327,6 @@
       <c r="J28" s="7" t="n"/>
       <c r="K28" s="7" t="n"/>
       <c r="L28" s="7" t="n"/>
-      <c r="M28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n"/>
@@ -7055,7 +6341,6 @@
       <c r="J29" s="7" t="n"/>
       <c r="K29" s="7" t="n"/>
       <c r="L29" s="7" t="n"/>
-      <c r="M29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n"/>
@@ -7070,7 +6355,6 @@
       <c r="J30" s="7" t="n"/>
       <c r="K30" s="7" t="n"/>
       <c r="L30" s="7" t="n"/>
-      <c r="M30" s="7" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n"/>
@@ -7085,7 +6369,6 @@
       <c r="J31" s="7" t="n"/>
       <c r="K31" s="7" t="n"/>
       <c r="L31" s="7" t="n"/>
-      <c r="M31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n"/>
@@ -7100,7 +6383,6 @@
       <c r="J32" s="7" t="n"/>
       <c r="K32" s="7" t="n"/>
       <c r="L32" s="7" t="n"/>
-      <c r="M32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n"/>
@@ -7115,7 +6397,6 @@
       <c r="J33" s="7" t="n"/>
       <c r="K33" s="7" t="n"/>
       <c r="L33" s="7" t="n"/>
-      <c r="M33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n"/>
@@ -7130,7 +6411,6 @@
       <c r="J34" s="7" t="n"/>
       <c r="K34" s="7" t="n"/>
       <c r="L34" s="7" t="n"/>
-      <c r="M34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n"/>
@@ -7145,7 +6425,6 @@
       <c r="J35" s="7" t="n"/>
       <c r="K35" s="7" t="n"/>
       <c r="L35" s="7" t="n"/>
-      <c r="M35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n"/>
@@ -7160,7 +6439,6 @@
       <c r="J36" s="7" t="n"/>
       <c r="K36" s="7" t="n"/>
       <c r="L36" s="7" t="n"/>
-      <c r="M36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n"/>
@@ -7175,7 +6453,6 @@
       <c r="J37" s="7" t="n"/>
       <c r="K37" s="7" t="n"/>
       <c r="L37" s="7" t="n"/>
-      <c r="M37" s="7" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n"/>
@@ -7190,7 +6467,6 @@
       <c r="J38" s="7" t="n"/>
       <c r="K38" s="7" t="n"/>
       <c r="L38" s="7" t="n"/>
-      <c r="M38" s="7" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n"/>
@@ -7205,7 +6481,6 @@
       <c r="J39" s="7" t="n"/>
       <c r="K39" s="7" t="n"/>
       <c r="L39" s="7" t="n"/>
-      <c r="M39" s="7" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n"/>
@@ -7220,7 +6495,6 @@
       <c r="J40" s="7" t="n"/>
       <c r="K40" s="7" t="n"/>
       <c r="L40" s="7" t="n"/>
-      <c r="M40" s="7" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n"/>
@@ -7235,7 +6509,6 @@
       <c r="J41" s="7" t="n"/>
       <c r="K41" s="7" t="n"/>
       <c r="L41" s="7" t="n"/>
-      <c r="M41" s="7" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n"/>
@@ -7250,7 +6523,6 @@
       <c r="J42" s="7" t="n"/>
       <c r="K42" s="7" t="n"/>
       <c r="L42" s="7" t="n"/>
-      <c r="M42" s="7" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n"/>
@@ -7265,7 +6537,6 @@
       <c r="J43" s="7" t="n"/>
       <c r="K43" s="7" t="n"/>
       <c r="L43" s="7" t="n"/>
-      <c r="M43" s="7" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n"/>
@@ -7280,7 +6551,6 @@
       <c r="J44" s="7" t="n"/>
       <c r="K44" s="7" t="n"/>
       <c r="L44" s="7" t="n"/>
-      <c r="M44" s="7" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n"/>
@@ -7295,7 +6565,6 @@
       <c r="J45" s="7" t="n"/>
       <c r="K45" s="7" t="n"/>
       <c r="L45" s="7" t="n"/>
-      <c r="M45" s="7" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n"/>
@@ -7310,7 +6579,6 @@
       <c r="J46" s="7" t="n"/>
       <c r="K46" s="7" t="n"/>
       <c r="L46" s="7" t="n"/>
-      <c r="M46" s="7" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n"/>
@@ -7325,7 +6593,6 @@
       <c r="J47" s="7" t="n"/>
       <c r="K47" s="7" t="n"/>
       <c r="L47" s="7" t="n"/>
-      <c r="M47" s="7" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n"/>
@@ -7340,7 +6607,6 @@
       <c r="J48" s="7" t="n"/>
       <c r="K48" s="7" t="n"/>
       <c r="L48" s="7" t="n"/>
-      <c r="M48" s="7" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n"/>
@@ -7355,7 +6621,6 @@
       <c r="J49" s="7" t="n"/>
       <c r="K49" s="7" t="n"/>
       <c r="L49" s="7" t="n"/>
-      <c r="M49" s="7" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n"/>
@@ -7370,7 +6635,6 @@
       <c r="J50" s="7" t="n"/>
       <c r="K50" s="7" t="n"/>
       <c r="L50" s="7" t="n"/>
-      <c r="M50" s="7" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n"/>
@@ -7385,7 +6649,6 @@
       <c r="J51" s="7" t="n"/>
       <c r="K51" s="7" t="n"/>
       <c r="L51" s="7" t="n"/>
-      <c r="M51" s="7" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n"/>
@@ -7400,7 +6663,6 @@
       <c r="J52" s="7" t="n"/>
       <c r="K52" s="7" t="n"/>
       <c r="L52" s="7" t="n"/>
-      <c r="M52" s="7" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n"/>
@@ -7415,7 +6677,6 @@
       <c r="J53" s="7" t="n"/>
       <c r="K53" s="7" t="n"/>
       <c r="L53" s="7" t="n"/>
-      <c r="M53" s="7" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n"/>
@@ -7430,7 +6691,6 @@
       <c r="J54" s="7" t="n"/>
       <c r="K54" s="7" t="n"/>
       <c r="L54" s="7" t="n"/>
-      <c r="M54" s="7" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n"/>
@@ -7445,7 +6705,6 @@
       <c r="J55" s="7" t="n"/>
       <c r="K55" s="7" t="n"/>
       <c r="L55" s="7" t="n"/>
-      <c r="M55" s="7" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n"/>
@@ -7460,7 +6719,6 @@
       <c r="J56" s="7" t="n"/>
       <c r="K56" s="7" t="n"/>
       <c r="L56" s="7" t="n"/>
-      <c r="M56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n"/>
@@ -7475,7 +6733,6 @@
       <c r="J57" s="7" t="n"/>
       <c r="K57" s="7" t="n"/>
       <c r="L57" s="7" t="n"/>
-      <c r="M57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n"/>
@@ -7490,7 +6747,6 @@
       <c r="J58" s="7" t="n"/>
       <c r="K58" s="7" t="n"/>
       <c r="L58" s="7" t="n"/>
-      <c r="M58" s="7" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n"/>
@@ -7505,7 +6761,6 @@
       <c r="J59" s="7" t="n"/>
       <c r="K59" s="7" t="n"/>
       <c r="L59" s="7" t="n"/>
-      <c r="M59" s="7" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n"/>
@@ -7520,7 +6775,6 @@
       <c r="J60" s="7" t="n"/>
       <c r="K60" s="7" t="n"/>
       <c r="L60" s="7" t="n"/>
-      <c r="M60" s="7" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n"/>
@@ -7535,7 +6789,6 @@
       <c r="J61" s="7" t="n"/>
       <c r="K61" s="7" t="n"/>
       <c r="L61" s="7" t="n"/>
-      <c r="M61" s="7" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n"/>
@@ -7550,7 +6803,6 @@
       <c r="J62" s="7" t="n"/>
       <c r="K62" s="7" t="n"/>
       <c r="L62" s="7" t="n"/>
-      <c r="M62" s="7" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n"/>
@@ -7565,7 +6817,6 @@
       <c r="J63" s="7" t="n"/>
       <c r="K63" s="7" t="n"/>
       <c r="L63" s="7" t="n"/>
-      <c r="M63" s="7" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n"/>
@@ -7580,7 +6831,6 @@
       <c r="J64" s="7" t="n"/>
       <c r="K64" s="7" t="n"/>
       <c r="L64" s="7" t="n"/>
-      <c r="M64" s="7" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n"/>
@@ -7595,7 +6845,6 @@
       <c r="J65" s="7" t="n"/>
       <c r="K65" s="7" t="n"/>
       <c r="L65" s="7" t="n"/>
-      <c r="M65" s="7" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n"/>
@@ -7610,7 +6859,6 @@
       <c r="J66" s="7" t="n"/>
       <c r="K66" s="7" t="n"/>
       <c r="L66" s="7" t="n"/>
-      <c r="M66" s="7" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n"/>
@@ -7625,7 +6873,6 @@
       <c r="J67" s="7" t="n"/>
       <c r="K67" s="7" t="n"/>
       <c r="L67" s="7" t="n"/>
-      <c r="M67" s="7" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n"/>
@@ -7640,7 +6887,6 @@
       <c r="J68" s="7" t="n"/>
       <c r="K68" s="7" t="n"/>
       <c r="L68" s="7" t="n"/>
-      <c r="M68" s="7" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n"/>
@@ -7655,7 +6901,6 @@
       <c r="J69" s="7" t="n"/>
       <c r="K69" s="7" t="n"/>
       <c r="L69" s="7" t="n"/>
-      <c r="M69" s="7" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n"/>
@@ -7670,7 +6915,6 @@
       <c r="J70" s="7" t="n"/>
       <c r="K70" s="7" t="n"/>
       <c r="L70" s="7" t="n"/>
-      <c r="M70" s="7" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n"/>
@@ -7685,7 +6929,6 @@
       <c r="J71" s="7" t="n"/>
       <c r="K71" s="7" t="n"/>
       <c r="L71" s="7" t="n"/>
-      <c r="M71" s="7" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n"/>
@@ -7700,7 +6943,6 @@
       <c r="J72" s="7" t="n"/>
       <c r="K72" s="7" t="n"/>
       <c r="L72" s="7" t="n"/>
-      <c r="M72" s="7" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n"/>
@@ -7715,7 +6957,6 @@
       <c r="J73" s="7" t="n"/>
       <c r="K73" s="7" t="n"/>
       <c r="L73" s="7" t="n"/>
-      <c r="M73" s="7" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n"/>
@@ -7730,7 +6971,6 @@
       <c r="J74" s="7" t="n"/>
       <c r="K74" s="7" t="n"/>
       <c r="L74" s="7" t="n"/>
-      <c r="M74" s="7" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n"/>
@@ -7745,7 +6985,6 @@
       <c r="J75" s="7" t="n"/>
       <c r="K75" s="7" t="n"/>
       <c r="L75" s="7" t="n"/>
-      <c r="M75" s="7" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n"/>
@@ -7760,7 +6999,6 @@
       <c r="J76" s="7" t="n"/>
       <c r="K76" s="7" t="n"/>
       <c r="L76" s="7" t="n"/>
-      <c r="M76" s="7" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n"/>
@@ -7775,7 +7013,6 @@
       <c r="J77" s="7" t="n"/>
       <c r="K77" s="7" t="n"/>
       <c r="L77" s="7" t="n"/>
-      <c r="M77" s="7" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n"/>
@@ -7790,7 +7027,6 @@
       <c r="J78" s="7" t="n"/>
       <c r="K78" s="7" t="n"/>
       <c r="L78" s="7" t="n"/>
-      <c r="M78" s="7" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n"/>
@@ -7805,7 +7041,6 @@
       <c r="J79" s="7" t="n"/>
       <c r="K79" s="7" t="n"/>
       <c r="L79" s="7" t="n"/>
-      <c r="M79" s="7" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n"/>
@@ -7820,7 +7055,6 @@
       <c r="J80" s="7" t="n"/>
       <c r="K80" s="7" t="n"/>
       <c r="L80" s="7" t="n"/>
-      <c r="M80" s="7" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n"/>
@@ -7835,7 +7069,6 @@
       <c r="J81" s="7" t="n"/>
       <c r="K81" s="7" t="n"/>
       <c r="L81" s="7" t="n"/>
-      <c r="M81" s="7" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n"/>
@@ -7850,7 +7083,6 @@
       <c r="J82" s="7" t="n"/>
       <c r="K82" s="7" t="n"/>
       <c r="L82" s="7" t="n"/>
-      <c r="M82" s="7" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n"/>
@@ -7865,7 +7097,6 @@
       <c r="J83" s="7" t="n"/>
       <c r="K83" s="7" t="n"/>
       <c r="L83" s="7" t="n"/>
-      <c r="M83" s="7" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n"/>
@@ -7880,7 +7111,6 @@
       <c r="J84" s="7" t="n"/>
       <c r="K84" s="7" t="n"/>
       <c r="L84" s="7" t="n"/>
-      <c r="M84" s="7" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n"/>
@@ -7895,7 +7125,6 @@
       <c r="J85" s="7" t="n"/>
       <c r="K85" s="7" t="n"/>
       <c r="L85" s="7" t="n"/>
-      <c r="M85" s="7" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n"/>
@@ -7910,7 +7139,6 @@
       <c r="J86" s="7" t="n"/>
       <c r="K86" s="7" t="n"/>
       <c r="L86" s="7" t="n"/>
-      <c r="M86" s="7" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n"/>
@@ -7925,7 +7153,6 @@
       <c r="J87" s="7" t="n"/>
       <c r="K87" s="7" t="n"/>
       <c r="L87" s="7" t="n"/>
-      <c r="M87" s="7" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n"/>
@@ -7940,7 +7167,6 @@
       <c r="J88" s="7" t="n"/>
       <c r="K88" s="7" t="n"/>
       <c r="L88" s="7" t="n"/>
-      <c r="M88" s="7" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n"/>
@@ -7955,7 +7181,6 @@
       <c r="J89" s="7" t="n"/>
       <c r="K89" s="7" t="n"/>
       <c r="L89" s="7" t="n"/>
-      <c r="M89" s="7" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n"/>
@@ -7970,7 +7195,6 @@
       <c r="J90" s="7" t="n"/>
       <c r="K90" s="7" t="n"/>
       <c r="L90" s="7" t="n"/>
-      <c r="M90" s="7" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n"/>
@@ -7985,7 +7209,6 @@
       <c r="J91" s="7" t="n"/>
       <c r="K91" s="7" t="n"/>
       <c r="L91" s="7" t="n"/>
-      <c r="M91" s="7" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n"/>
@@ -8000,7 +7223,6 @@
       <c r="J92" s="7" t="n"/>
       <c r="K92" s="7" t="n"/>
       <c r="L92" s="7" t="n"/>
-      <c r="M92" s="7" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="7" t="n"/>
@@ -8015,7 +7237,6 @@
       <c r="J93" s="7" t="n"/>
       <c r="K93" s="7" t="n"/>
       <c r="L93" s="7" t="n"/>
-      <c r="M93" s="7" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n"/>
@@ -8030,7 +7251,6 @@
       <c r="J94" s="7" t="n"/>
       <c r="K94" s="7" t="n"/>
       <c r="L94" s="7" t="n"/>
-      <c r="M94" s="7" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="7" t="n"/>
@@ -8045,7 +7265,6 @@
       <c r="J95" s="7" t="n"/>
       <c r="K95" s="7" t="n"/>
       <c r="L95" s="7" t="n"/>
-      <c r="M95" s="7" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n"/>
@@ -8060,7 +7279,6 @@
       <c r="J96" s="7" t="n"/>
       <c r="K96" s="7" t="n"/>
       <c r="L96" s="7" t="n"/>
-      <c r="M96" s="7" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="7" t="n"/>
@@ -8075,7 +7293,6 @@
       <c r="J97" s="7" t="n"/>
       <c r="K97" s="7" t="n"/>
       <c r="L97" s="7" t="n"/>
-      <c r="M97" s="7" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n"/>
@@ -8090,7 +7307,6 @@
       <c r="J98" s="7" t="n"/>
       <c r="K98" s="7" t="n"/>
       <c r="L98" s="7" t="n"/>
-      <c r="M98" s="7" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="7" t="n"/>
@@ -8105,7 +7321,6 @@
       <c r="J99" s="7" t="n"/>
       <c r="K99" s="7" t="n"/>
       <c r="L99" s="7" t="n"/>
-      <c r="M99" s="7" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n"/>
@@ -8120,7 +7335,6 @@
       <c r="J100" s="7" t="n"/>
       <c r="K100" s="7" t="n"/>
       <c r="L100" s="7" t="n"/>
-      <c r="M100" s="7" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="7" t="n"/>
@@ -8135,7 +7349,6 @@
       <c r="J101" s="7" t="n"/>
       <c r="K101" s="7" t="n"/>
       <c r="L101" s="7" t="n"/>
-      <c r="M101" s="7" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="7" t="n"/>
@@ -8150,7 +7363,6 @@
       <c r="J102" s="7" t="n"/>
       <c r="K102" s="7" t="n"/>
       <c r="L102" s="7" t="n"/>
-      <c r="M102" s="7" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="7" t="n"/>
@@ -8165,7 +7377,6 @@
       <c r="J103" s="7" t="n"/>
       <c r="K103" s="7" t="n"/>
       <c r="L103" s="7" t="n"/>
-      <c r="M103" s="7" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="7" t="n"/>
@@ -8180,7 +7391,6 @@
       <c r="J104" s="7" t="n"/>
       <c r="K104" s="7" t="n"/>
       <c r="L104" s="7" t="n"/>
-      <c r="M104" s="7" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="7" t="n"/>
@@ -8195,7 +7405,6 @@
       <c r="J105" s="7" t="n"/>
       <c r="K105" s="7" t="n"/>
       <c r="L105" s="7" t="n"/>
-      <c r="M105" s="7" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="7" t="n"/>
@@ -8210,7 +7419,6 @@
       <c r="J106" s="7" t="n"/>
       <c r="K106" s="7" t="n"/>
       <c r="L106" s="7" t="n"/>
-      <c r="M106" s="7" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="7" t="n"/>
@@ -8225,7 +7433,6 @@
       <c r="J107" s="7" t="n"/>
       <c r="K107" s="7" t="n"/>
       <c r="L107" s="7" t="n"/>
-      <c r="M107" s="7" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="7" t="n"/>
@@ -8240,7 +7447,6 @@
       <c r="J108" s="7" t="n"/>
       <c r="K108" s="7" t="n"/>
       <c r="L108" s="7" t="n"/>
-      <c r="M108" s="7" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="7" t="n"/>
@@ -8255,7 +7461,6 @@
       <c r="J109" s="7" t="n"/>
       <c r="K109" s="7" t="n"/>
       <c r="L109" s="7" t="n"/>
-      <c r="M109" s="7" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="7" t="n"/>
@@ -8270,7 +7475,6 @@
       <c r="J110" s="7" t="n"/>
       <c r="K110" s="7" t="n"/>
       <c r="L110" s="7" t="n"/>
-      <c r="M110" s="7" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="7" t="n"/>
@@ -8285,7 +7489,6 @@
       <c r="J111" s="7" t="n"/>
       <c r="K111" s="7" t="n"/>
       <c r="L111" s="7" t="n"/>
-      <c r="M111" s="7" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="7" t="n"/>
@@ -8300,7 +7503,6 @@
       <c r="J112" s="7" t="n"/>
       <c r="K112" s="7" t="n"/>
       <c r="L112" s="7" t="n"/>
-      <c r="M112" s="7" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="7" t="n"/>
@@ -8315,7 +7517,6 @@
       <c r="J113" s="7" t="n"/>
       <c r="K113" s="7" t="n"/>
       <c r="L113" s="7" t="n"/>
-      <c r="M113" s="7" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="7" t="n"/>
@@ -8330,7 +7531,6 @@
       <c r="J114" s="7" t="n"/>
       <c r="K114" s="7" t="n"/>
       <c r="L114" s="7" t="n"/>
-      <c r="M114" s="7" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="7" t="n"/>
@@ -8345,7 +7545,6 @@
       <c r="J115" s="7" t="n"/>
       <c r="K115" s="7" t="n"/>
       <c r="L115" s="7" t="n"/>
-      <c r="M115" s="7" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="7" t="n"/>
@@ -8360,7 +7559,6 @@
       <c r="J116" s="7" t="n"/>
       <c r="K116" s="7" t="n"/>
       <c r="L116" s="7" t="n"/>
-      <c r="M116" s="7" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="7" t="n"/>
@@ -8375,7 +7573,6 @@
       <c r="J117" s="7" t="n"/>
       <c r="K117" s="7" t="n"/>
       <c r="L117" s="7" t="n"/>
-      <c r="M117" s="7" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="7" t="n"/>
@@ -8390,7 +7587,6 @@
       <c r="J118" s="7" t="n"/>
       <c r="K118" s="7" t="n"/>
       <c r="L118" s="7" t="n"/>
-      <c r="M118" s="7" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="7" t="n"/>
@@ -8405,7 +7601,6 @@
       <c r="J119" s="7" t="n"/>
       <c r="K119" s="7" t="n"/>
       <c r="L119" s="7" t="n"/>
-      <c r="M119" s="7" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="7" t="n"/>
@@ -8420,7 +7615,6 @@
       <c r="J120" s="7" t="n"/>
       <c r="K120" s="7" t="n"/>
       <c r="L120" s="7" t="n"/>
-      <c r="M120" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -8466,7 +7660,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
